--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G374"/>
+  <dimension ref="A1:G387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6382,8 +6382,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
-        <v>233</v>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -6402,13 +6404,44 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;ul&gt;
-	&lt;li&gt;ÍNDICES DE LIQUIDEZ &lt;ul&gt; &lt;li&gt;Índice de liquidez corrente = Ativo circulante/Passivo circulante&lt;/li&gt; &lt;li&gt;Indice de liquidez seca = (Ativo circulante – Estoques)/Passivo circulante&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;ÍNDICES DE ATIVIDADE &lt;ul&gt; &lt;li&gt;Giro do estoque = Custo das mercadorias vendidas/Estoque&lt;/li&gt; &lt;li&gt;Prazo médio de recebimento = Contas a receber de clientes/Valor diário médio das vendas&lt;/li&gt; &lt;li&gt;Prazo médio de recebimento = (Contas a receber de clientes x 360)/Vendas anuais&lt;/li&gt; &lt;li&gt;Prazo médio de pagamento = Fornecedores/Valor diário médio das compras&lt;/li&gt; &lt;li&gt;Prazo médio de pagamento = (Fornecedore x 360)/Compras anuais&lt;/li&gt; &lt;li&gt;Giro do ativo total = Vendas/Ativo total&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;ÍNDICES DE ENDIVIDAMENTO &lt;ul&gt; &lt;li&gt;Índice de endividamento geral = Passivo total/Ativo total&lt;/li&gt; &lt;li&gt;Índice de cobertura de juros = Lucro antes de juros e imposto de renda/Juros&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;ÍNDICES DE RENTABILIDADE &lt;ul&gt; &lt;li&gt;Margem de lucro bruto = (Receita de vendas – Custo das mercadorias vendidas)/Receita de vendas = Lucro bruto/Receita de vendas&lt;/li&gt; &lt;li&gt;Margem de lucro operacional = Lucro operacional/Receita de vendas&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;
-</t>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;strong&gt;ÍNDICES DE LIQUIDEZ&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Índice de liquidez corrente = $\frac{Ativo\ circulante}{Passivo\ circulante}$&lt;/li&gt;
+            &lt;li&gt;Índice de liquidez seca = $\frac{Ativo\ circulante\ –\ Estoques}{Passivo\ circulante}$&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;ÍNDICES DE ATIVIDADE&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Giro do estoque = $\frac{Custo\ das\ mercadorias\ vendidas}{Estoque}$&lt;/li&gt;
+            &lt;li&gt;Prazo médio de recebimento = $\frac{Contas\ a\ receber\ de\ clientes}{Valor\ diário\ médio\ das\ vendas}$&lt;/li&gt;
+            &lt;li&gt;Prazo médio de pagamento = $\frac{Fornecedores}{Valor\ diário\ médio\ das\ compras}$&lt;/li&gt;
+            &lt;li&gt;Giro do ativo total = $\frac{Vendas}{Ativo\ total}$&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;ÍNDICES DE ENDIVIDAMENTO&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Índice de endividamento geral = $\frac{Passivo\ total}{Ativo\ total}$&lt;/li&gt;
+            &lt;li&gt;Índice de cobertura de juros = $\frac{Lucro\ antes\ de\ juros\ e\ imposto\ de\ renda}{Juros}$&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;ÍNDICES DE RENTABILIDADE E RETORNO&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Margem de lucro bruto = $\frac{Lucro\ bruto}{Receita\ de\ vendas}$&lt;/li&gt;
+            &lt;li&gt;Margem de lucro operacional = $\frac{Lucro\ operacional}{Receita\ de\ vendas}$&lt;/li&gt;
+            &lt;li&gt;&lt;strong&gt;ROE (&lt;i&gt;Return on Equity&lt;/i&gt; / Retorno do Patrimônio Líquido)&lt;/strong&gt; = $\frac{Lucro\ L\acute{\imath}quido}{Patrim\hat{o}nio\ L\acute{\imath}quido}$
+                &lt;ul&gt;
+                    &lt;li&gt;indica o resultado alcançado com os investimentos realizados pelos acionistas ordinários&lt;/li&gt;
+                &lt;/ul&gt;
+            &lt;/li&gt;
+            &lt;li&gt;&lt;strong&gt;ROA (&lt;i&gt;Return on Assets&lt;/i&gt; / Retorno sobre o Ativo)&lt;/strong&gt; = $\frac{Lucro\ L\acute{\imath}quido}{Ativo\ Total}$
+                &lt;ul&gt;
+                    &lt;li&gt;indica a eficiência global no uso dos ativos pela gestão da empresa&lt;/li&gt;
+                &lt;/ul&gt;
+            &lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -14881,8 +14914,10 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="n">
-        <v>352</v>
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -14902,7 +14937,7 @@
       <c r="E259" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Conceito CAPM (Capital Asset Pricing Model)&lt;/strong&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito CAPM&lt;/strong&gt;
     &lt;ul&gt;
       &lt;li&gt;Modelo que determina o retorno esperado de um investimento com base no risco sistêmico.&lt;/li&gt;
       &lt;li&gt;Fórmula: $E[R] = R_f + \beta \cdot (R_m - R_f)$.&lt;/li&gt;
@@ -14911,19 +14946,24 @@
   &lt;li&gt;&lt;strong&gt;Cálculo para Carteiras (Portfólio)&lt;/strong&gt;
     &lt;ul&gt;
       &lt;li&gt;O Beta da carteira é a média ponderada dos Betas individuais.&lt;/li&gt;
-      &lt;li&gt;$\beta_{carteira} = (\% \text{Ativo A} \cdot \beta_A) + (\% \text{Ativo B} \cdot \beta_B)$.&lt;/li&gt;
+      &lt;li&gt;$\beta_{carteira} = (\%\ Ativo\ A \cdot \beta_A) + (\%\ Ativo\ B \cdot \beta_B)$.&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;&lt;strong&gt;Premissas Importantes&lt;/strong&gt;
     &lt;ul&gt;
       &lt;li&gt;&lt;strong&gt;Taxa Livre de Risco ($R_f$):&lt;/strong&gt; Retorno de ativos sem risco de crédito.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Beta ($\beta$):&lt;/strong&gt; Se &gt; 1, o ativo é mais volátil que o mercado; se &lt; 1, é mais defensivo.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Prêmio de Risco:&lt;/strong&gt; A diferença $(R_m - R_f)$ representa a compensação por correr risco de mercado.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Beta ($\beta$):&lt;/strong&gt; Risco sistêmico comparado ao mercado (onde mercado = 1).
+        &lt;ul&gt;
+            &lt;li&gt;se $\beta &gt; 1$: ativo agressivo e mais volátil que o mercado (ex: se o risco for 30% superior ao do mercado, $\beta = 1,3$).&lt;/li&gt;
+            &lt;li&gt;se $\beta &lt; 1$: ativo defensivo e menos volátil que o mercado.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Prêmio de Risco:&lt;/strong&gt; A diferença $(R_m - R_f)$ representa a compensação global por correr risco de mercado.&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;&lt;strong&gt;Dica para Concursos:&lt;/strong&gt;
     &lt;ul&gt;
-      &lt;li&gt;Cuidado para não confundir "Retorno de Mercado" ($R_m$) com "Prêmio de Risco" ($R_m - R_f$). A questão já deu a diferença (o prêmio) de 10%, facilitando o cálculo.&lt;/li&gt;
+      &lt;li&gt;Cuidado para não confundir "Retorno de Mercado" ($R_m$) com "Prêmio de Risco" ($R_m - R_f$). Se o enunciado fornece o "prêmio pelo risco", você deve multiplicar o Beta diretamente por esse valor, sem subtrair o $R_f$ dentro do parênteses.&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -21398,6 +21438,651 @@
         <v>0</v>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>469</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Curva de Phillips (Curto e Longo Prazo)</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;strong&gt;Conceito Central&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;relaciona as taxas de inflação e desemprego em uma economia&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;Curto Prazo&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;curva negativamente inclinada (presença de &lt;i&gt;trade-off&lt;/i&gt;)&lt;/li&gt;
+            &lt;li&gt;maior inflação resulta em menor desemprego (e vice-versa)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;Longo Prazo&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;não há &lt;i&gt;trade-off&lt;/i&gt; (escolha) entre inflação e desemprego&lt;/li&gt;
+            &lt;li&gt;curva é uma reta &lt;strong&gt;vertical&lt;/strong&gt;&lt;/li&gt;
+            &lt;li&gt;posicionada na &lt;b&gt;Taxa Natural de Desemprego (NAIRU - &lt;i&gt;Non-Accelerating Inflation Rate of Unemployment&lt;/i&gt; / Taxa de Desemprego Não Aceleradora da Inflação)&lt;/b&gt;&lt;/li&gt;
+            &lt;li&gt;a inflação não afeta o nível de emprego estrutural&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>470</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Elasticidade-Preço da Demanda (EPD)</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;strong&gt;Definição&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;mede a sensibilidade da quantidade demandada de um bem frente a variações no seu preço&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;Fórmula Base&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;$EPD = |\frac{\%\ Varia\c{c}\tilde{a}o\ na\ Quantidade}{\%\ Varia\c{c}\tilde{a}o\ no\ Pre\c{c}o}|$&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;Classificação do Resultado (Sempre em Módulo)&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;&lt;strong&gt;Elástica ($EPD &gt; 1$):&lt;/strong&gt; quantidade varia em proporção &lt;b&gt;maior&lt;/b&gt; que o preço (comum em bens supérfluos)&lt;/li&gt;
+            &lt;li&gt;&lt;strong&gt;Inelástica ($EPD &lt; 1$):&lt;/strong&gt; quantidade varia em proporção &lt;b&gt;menor&lt;/b&gt; que o preço (comum em bens essenciais)&lt;/li&gt;
+            &lt;li&gt;&lt;strong&gt;Unitária ($EPD = 1$):&lt;/strong&gt; variações proporcionais exatas&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;Lógica de Cálculo&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;se o preço de um serviço aumenta 25% e a demanda cai 10%, o módulo da divisão é $|-10\% / +25\%| = |-0,4| = 0,4$. A demanda é inelástica.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>471</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Índices de Inflação: IPC vs. Deflator do PIB</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;strong&gt;Índice de Preços ao Consumidor (IPC)&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;mede o custo de uma cesta &lt;b&gt;fixa&lt;/b&gt; de bens e serviços&lt;/li&gt;
+            &lt;li&gt;foco: produtos comprados por consumidores representativos (famílias)&lt;/li&gt;
+            &lt;li&gt;inclui &lt;b&gt;bens importados&lt;/b&gt; (desde que consumidos pelas famílias e presentes na cesta)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;Deflator do PIB (Produto Interno Bruto)&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;mede o custo de todos os bens e serviços finais produzidos internamente no país&lt;/li&gt;
+            &lt;li&gt;cesta &lt;b&gt;variável&lt;/b&gt; (muda anualmente conforme a produção da economia)&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;não&lt;/b&gt; considera bens importados (pois não fazem parte da produção nacional)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>0</v>
+      </c>
+      <c r="G377" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>472</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Economias e Deseconomias de Escala</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;strong&gt;Economia de Escala&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;ocorre no &lt;b&gt;longo prazo&lt;/b&gt;&lt;/li&gt;
+            &lt;li&gt;o Custo Total Médio (CTMe) &lt;b&gt;cai&lt;/b&gt; à medida que a quantidade produzida aumenta&lt;/li&gt;
+            &lt;li&gt;resultado da diluição dos custos fixos em um volume maior de produção&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;Deseconomia de Escala&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;o Custo Total Médio (CTMe) &lt;b&gt;sobe&lt;/b&gt; com o aumento extremo da produção&lt;/li&gt;
+            &lt;li&gt;causada por ineficiências gerenciais, gargalos logísticos ou burocracia excessiva devido ao tamanho da operação&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;Retornos Constantes de Escala&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;o Custo Total Médio (CTMe) se mantém &lt;b&gt;constante&lt;/b&gt; com a variação da produção&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>0</v>
+      </c>
+      <c r="G378" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>473</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Alavancagem Operacional e Financeira</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;strong&gt;Alavancagem Operacional&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;relação direta com o aumento da estrutura de &lt;b&gt;Custos Fixos&lt;/b&gt; (ex: investir em expansão de capacidade produtiva fixa)&lt;/li&gt;
+            &lt;li&gt;&lt;strong&gt;Impactos e Riscos:&lt;/strong&gt;
+                &lt;ul&gt;
+                    &lt;li&gt;aumenta o Ponto de Equilíbrio&lt;/li&gt;
+                    &lt;li&gt;eleva o &lt;b&gt;Risco Operacional&lt;/b&gt; da empresa&lt;/li&gt;
+                    &lt;li&gt;pequenas variações no volume de vendas passam a causar variações proporcionalmente maiores no lucro&lt;/li&gt;
+                &lt;/ul&gt;
+            &lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;strong&gt;Alavancagem Financeira&lt;/strong&gt;
+        &lt;ul&gt;
+            &lt;li&gt;relação com o uso de &lt;b&gt;Capital de Terceiros&lt;/b&gt; (dívidas) na estrutura de financiamento&lt;/li&gt;
+            &lt;li&gt;&lt;strong&gt;Impactos e Riscos:&lt;/strong&gt;
+                &lt;ul&gt;
+                    &lt;li&gt;busca aumentar o retorno para o capital dos acionistas&lt;/li&gt;
+                    &lt;li&gt;aumenta o &lt;b&gt;Risco Financeiro&lt;/b&gt; devido à obrigatoriedade do pagamento de juros fixos&lt;/li&gt;
+                &lt;/ul&gt;
+            &lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>0</v>
+      </c>
+      <c r="G379" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Operações de Desconto</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Operações de Desconto: Teoria e Relações Conceituais</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceitos Iniciais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Valor Nominal ($N$):&lt;/strong&gt; valor de face ou valor futuro do título[cite: 4].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Valor Atual ($A$):&lt;/strong&gt; valor recebido antecipadamente, também designado Valor Descontado ou Valor Presente[cite: 4].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Desconto ($D$):&lt;/strong&gt; diferença absoluta entre o Valor Nominal e o Valor Atual ($D=N-A$)[cite: 4].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Desconto Racional (Por Dentro)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;a taxa de desconto incide sobre o &lt;strong&gt;Valor Atual&lt;/strong&gt; do título[cite: 6].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Desconto Comercial / Bancário (Por Fora)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;a taxa de desconto incide sobre o &lt;strong&gt;Valor Nominal&lt;/strong&gt; do título[cite: 6].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Relação Conceitual (Mesmo título, taxa e prazo)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;o Desconto Comercial será sempre &lt;strong&gt;maior&lt;/strong&gt; que o Desconto Racional ($D_{CS}&gt;D_{RS}$)[cite: 22, 26].&lt;/li&gt;
+      &lt;li&gt;o Valor Atual no Desconto Comercial será sempre &lt;strong&gt;menor&lt;/strong&gt; que o Valor Atual no Desconto Racional ($A_{CS}&lt;A_{RS}$)[cite: 22, 26].&lt;/li&gt;
+      &lt;li&gt;o Desconto Racional revela-se mais vantajoso para o proprietário do título, dado que proporciona um Valor Atual superior[cite: 24].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>0</v>
+      </c>
+      <c r="G380" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Operações de Desconto</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Fórmulas de Desconto Simples</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Desconto Racional Simples (Por Dentro)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Fórmula do Desconto:&lt;/strong&gt; $D_{RS}=A \times i \times t$[cite: 6, 25].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=\frac{N}{(1+i \times t)}$[cite: 6, 25].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Desconto Comercial Simples (Por Fora)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Fórmula do Desconto:&lt;/strong&gt; $D_{CS}=N \times i \times t$[cite: 7, 25].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=N \times (1-i \times t)$[cite: 7, 25].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Relação Matemática entre os Descontos Simples&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;conhecendo um dos descontos, pode obter-se o outro através da expressão: $D_{CS}=D_{RS} \times (1+i \times t)$[cite: 11, 25].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>0</v>
+      </c>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Operações de Desconto</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Fórmulas de Desconto Composto</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Desconto Racional Composto (Por Dentro)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=\frac{N}{(1+i)^t}$[cite: 14, 25].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Cálculo do Desconto:&lt;/strong&gt; $D_{RC}=N-A$[cite: 14, 25].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Desconto Comercial Composto (Por Fora)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=N \times (1-i)^t$[cite: 14, 25].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Cálculo do Desconto:&lt;/strong&gt; $D_{CC}=N-A$[cite: 14, 25].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>0</v>
+      </c>
+      <c r="G382" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Equivalência de Capitais</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Equivalência de Capitais e Deslocamento no Tempo</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito Base&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;dois ou mais capitais com datas de resgate distintas são equivalentes se, ao serem transportados para uma mesma data focal à mesma taxa de juros, originarem valores idênticos[cite: 64, 87].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Regras de Deslocamento Temporal&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Deslocar para o futuro (Direita / Capitalização):&lt;/strong&gt; multiplica-se a parcela por $(1+i)^t$ em juros compostos, ou por $(1+i \times t)$ em juros simples[cite: 63, 87].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Deslocar para o passado (Esquerda / Descapitalização):&lt;/strong&gt; divide-se a parcela por $(1+i)^t$ em juros compostos, ou por $(1+i \times t)$ em juros simples[cite: 63, 87].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Propriedade Fundamental (Juros Compostos)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;em regime de Juros Compostos, a comparação e a equivalência de capitais &lt;strong&gt;não dependem&lt;/strong&gt; da data focal escolhida[cite: 64, 88]. Qualquer data na linha temporal validará a equivalência[cite: 64].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>0</v>
+      </c>
+      <c r="G383" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>479</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Operações de Desconto</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Taxa Efetiva em Operações de Desconto</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito de Taxa Efetiva&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;é a taxa de juros que, ao ser aplicada sobre o Valor Atual, gera o Valor Nominal no período considerado[cite: 18, 23].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Característica do Desconto Comercial&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;a taxa de desconto comercial &lt;strong&gt;não é&lt;/strong&gt; uma taxa efetiva, dado que incide sobre o Valor Nominal[cite: 19, 24].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Fórmula de Conversão (Desconto Comercial Simples)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;$i_{ef}=\frac{i_{cs}}{1-i_{cs} \times t}$[cite: 18, 25].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>0</v>
+      </c>
+      <c r="G384" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>480</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Equivalência de Capitais</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Rendas Uniformes (Séries de Pagamento): Valor Atual (VA)</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito de Rendas Uniformes (Certas)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;sequência de fluxos de caixa em intervalos de tempo iguais, com parcelas constantes[cite: 70, 88].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Valor Atual de Rendas Postecipadas (Fim do período)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;$VA=P \times \left[ \frac{(1+i)^n-1}{i \times (1+i)^n} \right]$ ou $VA=P \times \left[ \frac{1-(1+i)^{-n}}{i} \right]$[cite: 71, 88].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Fator de Valor Atual:&lt;/strong&gt; $a_{n-i}=\left[ \frac{(1+i)^n-1}{i \times (1+i)^n} \right]$[cite: 73, 88]. O Fator de Recuperação de Capital (FRC) é o seu inverso: $FRC=\frac{1}{a_{n-i}}$[cite: 73, 88].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Valor Atual de Rendas Antecipadas (Início do período)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;a fórmula é idêntica à das rendas postecipadas, sendo no final multiplicada pelo fator de capitalização $(1+i)$[cite: 77, 88].&lt;/li&gt;
+      &lt;li&gt;$VA=P \times \left[ \frac{(1+i)^n-1}{i \times (1+i)^n} \right] \times (1+i)$[cite: 77].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>0</v>
+      </c>
+      <c r="G385" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>481</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Equivalência de Capitais</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Rendas Uniformes (Séries de Pagamento): Valor Futuro (VF)</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Valor Futuro de Rendas Postecipadas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;$VF=P \times \left[ \frac{(1+i)^n-1}{i} \right]$[cite: 74, 88].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Fator de Valor Futuro (Acumulação):&lt;/strong&gt; $S_{n-i}=\left[ \frac{(1+i)^n-1}{i} \right]$[cite: 76, 89]. O Fator de Formação de Capital (FFC) é o seu inverso: $FFC=\frac{1}{S_{n-i}}$[cite: 76, 89].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Valor Futuro de Rendas Antecipadas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;a expressão matemática do Valor Futuro para uma série antecipada é &lt;strong&gt;igual&lt;/strong&gt; à da série postecipada[cite: 78].&lt;/li&gt;
+      &lt;li&gt;a multiplicação adicional pelo fator $(1+i)$ verifica-se apenas no cálculo do Valor Atual[cite: 78].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>482</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Equivalência de Capitais</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Rendas Perpétuas (Termos Ilimitados)</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;fluxos de duração infinita, ou seja, sem um número de prestações passível de determinação exata[cite: 83, 89]. Na ausência de especificação no problema, assume-se a modalidade postecipada[cite: 84].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Fórmulas do Valor Atual (VA)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Postecipadas:&lt;/strong&gt; $VA=\frac{P}{i}$[cite: 83, 89].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Postecipadas com crescimento ($g$):&lt;/strong&gt; $VA=\frac{P}{i-g}$[cite: 83, 89].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Antecipadas:&lt;/strong&gt; $VA=\frac{P}{i} \times (1+i)$[cite: 84, 89].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G410"/>
+  <dimension ref="A1:G412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23532,6 +23532,109 @@
         <v>0</v>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>508</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Distribuição Física (Outbound Logistics)</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Conceito Central&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;trata da movimentação, estocagem e processamento de pedidos dos &lt;b&gt;produtos finais&lt;/b&gt; (acabados) da firma&lt;/li&gt;
+            &lt;li&gt;foca no fluxo de saída: inicia na liberação da esteira de montagem fabril e vai até a entrega ao mercado/consumidor final&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Fronteiras e Escopo (Pegadinhas de Prova)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;não engloba o fluxo de entrada (recebimento de matérias-primas e insumos), que é função do Suprimento Físico (&lt;i&gt;Inbound Logistics&lt;/i&gt; / Administração de Materiais)&lt;/li&gt;
+            &lt;li&gt;não engloba a fabricação ou transformação da matéria-prima (Produção/Manufatura)&lt;/li&gt;
+            &lt;li&gt;é estruturada para &lt;b&gt;apoiar&lt;/b&gt; o Canal de Distribuição (este foca nas relações de vendas, marketing e troca de posse, sendo planejado primeiro)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Logística Empresarial Integrada&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;busca a unificação gerencial e de planejamento das frentes de abastecimento (&lt;i&gt;inbound&lt;/i&gt;) com a frente de distribuição física (&lt;i&gt;outbound&lt;/i&gt;)&lt;/li&gt;
+            &lt;li&gt;ambos os canais (suprimento e distribuição) apresentam grandes similaridades em suas atividades&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>0</v>
+      </c>
+      <c r="G411" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>509</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Logística de Suprimentos (Inbound Logistics / Administração de Materiais)</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Conceito Central&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;trata do fluxo de materiais, insumos e matérias-primas &lt;b&gt;dos fornecedores para a empresa&lt;/b&gt;&lt;/li&gt;
+            &lt;li&gt;foco no fluxo de entrada: vai da aquisição estruturada até a disponibilização do material para o início do processo de produção (manufatura)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Principais Atividades&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;seleção e negociação com fornecedores (compras / &lt;i&gt;procurement&lt;/i&gt;)&lt;/li&gt;
+            &lt;li&gt;transporte de suprimentos (da origem até a fábrica)&lt;/li&gt;
+            &lt;li&gt;recebimento e controle de qualidade de insumos&lt;/li&gt;
+            &lt;li&gt;armazenagem e gestão de estoques de matérias-primas&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Diferença Crucial (Inbound vs. Outbound)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;&lt;b&gt;Inbound:&lt;/b&gt; movimenta o que a empresa &lt;i&gt;precisa para produzir&lt;/i&gt; (foco na relação a montante / &lt;i&gt;upstream&lt;/i&gt; com fornecedores).&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;Outbound:&lt;/b&gt; movimenta o que a empresa &lt;i&gt;já produziu&lt;/i&gt; (foco na relação a jusante / &lt;i&gt;downstream&lt;/i&gt; com clientes).&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>0</v>
+      </c>
+      <c r="G412" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -18526,8 +18526,10 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="n">
-        <v>467</v>
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>467</t>
+        </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -18547,60 +18549,29 @@
       <c r="E318" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;&lt;b&gt;Conceito&lt;/b&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Expressões que indicam parte de um todo
-        &lt;ul&gt;
-          &lt;li&gt;Ex: &lt;i&gt;a maioria de, a maior parte de, grande parte de, uma porção de, o resto de, metade de&lt;/i&gt;&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;Geralmente acompanhadas de um determinante (especificador)&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;b&gt;Regras de Concordância Verbal&lt;/b&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;b&gt;Determinante no Plural&lt;/b&gt; (Ex: &lt;i&gt;"dos alunos"&lt;/i&gt;)
-        &lt;ul&gt;
-          &lt;li&gt;A concordância é &lt;b&gt;facultativa&lt;/b&gt; (ambas as formas são corretas)&lt;/li&gt;
-          &lt;li&gt;&lt;b&gt;Concordância Gramatical (Rigorosa):&lt;/b&gt;
-            &lt;ul&gt;
-              &lt;li&gt;Verbo concorda com o &lt;b&gt;núcleo&lt;/b&gt; singular da expressão partitiva&lt;/li&gt;
-              &lt;li&gt;Ex: &lt;i&gt;A maioria dos candidatos &lt;u&gt;foi&lt;/u&gt; aprovada.&lt;/i&gt;&lt;/li&gt;
-            &lt;/ul&gt;
-          &lt;/li&gt;
-          &lt;li&gt;&lt;b&gt;Concordância Ideológica (Atrativa / Silepse de Número):&lt;/b&gt;
-            &lt;ul&gt;
-              &lt;li&gt;Verbo concorda com o &lt;b&gt;determinante&lt;/b&gt; no plural&lt;/li&gt;
-              &lt;li&gt;Ex: &lt;i&gt;A maioria dos candidatos &lt;u&gt;foram&lt;/u&gt; aprovados.&lt;/i&gt;&lt;/li&gt;
-            &lt;/ul&gt;
-          &lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;&lt;b&gt;Determinante no Singular ou Inexistente&lt;/b&gt; (Ex: &lt;i&gt;"do grupo"&lt;/i&gt;)
-        &lt;ul&gt;
-          &lt;li&gt;A concordância é &lt;b&gt;obrigatoriamente&lt;/b&gt; no singular&lt;/li&gt;
-          &lt;li&gt;Ex: &lt;i&gt;A maior parte da população &lt;u&gt;votou&lt;/u&gt;.&lt;/i&gt;&lt;/li&gt;
-          &lt;li&gt;Ex: &lt;i&gt;A maioria &lt;u&gt;decidiu&lt;/u&gt; ir embora.&lt;/i&gt;&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;b&gt;Expressões Correlatas (Mesma Lógica)&lt;/b&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;b&gt;Coletivos Partitivos&lt;/b&gt;
-        &lt;ul&gt;
-          &lt;li&gt;Ex: &lt;i&gt;um bando de, uma multidão de, um grupo de&lt;/i&gt;&lt;/li&gt;
-          &lt;li&gt;Seguem a mesma regra facultativa se o determinante for plural&lt;/li&gt;
-          &lt;li&gt;Ex: &lt;i&gt;Uma multidão de fãs &lt;u&gt;gritou / gritaram&lt;/u&gt;.&lt;/i&gt;&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;&lt;b&gt;Porcentagens e Frações&lt;/b&gt;
-        &lt;ul&gt;
-          &lt;li&gt;Verbo pode concordar com o &lt;b&gt;número&lt;/b&gt; ou com o &lt;b&gt;determinante&lt;/b&gt;&lt;/li&gt;
-          &lt;li&gt;Ex: &lt;i&gt;1% dos alunos &lt;u&gt;faltou / faltaram&lt;/u&gt;.&lt;/i&gt;&lt;/li&gt;
-          &lt;li&gt;Atenção: Se não houver determinante, concorda estritamente com o número (Ex: &lt;i&gt;1% &lt;u&gt;faltou&lt;/u&gt; / 2% &lt;u&gt;faltaram&lt;/u&gt;&lt;/i&gt;).&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;A Estrutura do Sujeito Partitivo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;O sujeito é formado por duas partes: o &lt;b&gt;Núcleo&lt;/b&gt; (ex: &lt;i&gt;A maioria&lt;/i&gt; - sempre singular) e o &lt;b&gt;Determinante&lt;/b&gt; (ex: &lt;i&gt;dos candidatos&lt;/i&gt; - que pode ser plural ou singular).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Regra 1: Determinante no Plural&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;A concordância é &lt;b&gt;facultativa&lt;/b&gt;. Você tem dois caminhos igualmente corretos na prova:&lt;/li&gt;
+      &lt;li&gt;&lt;b&gt;Caminho 1 (Concordar com o Núcleo):&lt;/b&gt; O verbo fica no singular. &lt;i&gt;Ex: A &lt;u&gt;maioria&lt;/u&gt; dos candidatos &lt;u&gt;foi&lt;/u&gt; aprovada.&lt;/i&gt;&lt;/li&gt;
+      &lt;li&gt;&lt;b&gt;Caminho 2 (Concordar com o Determinante):&lt;/b&gt; O verbo fica no plural, atraído pela proximidade. &lt;i&gt;Ex: A maioria dos &lt;u&gt;candidatos foram&lt;/u&gt; aprovados.&lt;/i&gt;&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Regra 2: Determinante no Singular (ou Inexistente)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;A concordância é &lt;b&gt;obrigatória no singular&lt;/b&gt;. Como não existe nenhuma palavra no plural para atrair o verbo, a regra facultativa deixa de existir.&lt;/li&gt;
+      &lt;li&gt;&lt;i&gt;Ex: A maior parte &lt;u&gt;da população votou&lt;/u&gt;.&lt;/i&gt;&lt;/li&gt;
+      &lt;li&gt;&lt;i&gt;Ex: A maioria &lt;u&gt;decidiu&lt;/u&gt; ir embora.&lt;/i&gt;&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Expressões Correlatas (Mesma Lógica)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;b&gt;Coletivos Partitivos:&lt;/b&gt; &lt;i&gt;um bando de, uma multidão de, um grupo de.&lt;/i&gt; Seguem a mesma regra facultativa se o determinante for plural. &lt;i&gt;Ex: Uma multidão de fãs &lt;u&gt;gritou / gritaram&lt;/u&gt;.&lt;/i&gt;&lt;/li&gt;
+      &lt;li&gt;&lt;b&gt;Porcentagens e Frações:&lt;/b&gt; O verbo pode concordar com o número ou com o determinante. &lt;i&gt;Ex: 1% dos alunos &lt;u&gt;faltou / faltaram&lt;/u&gt;.&lt;/i&gt; (Se não houver determinante, concorda estritamente com o número: &lt;i&gt;1% &lt;u&gt;faltou&lt;/u&gt; / 2% &lt;u&gt;faltaram&lt;/u&gt;&lt;/i&gt;).&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G360"/>
+  <dimension ref="A1:G361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19628,8 +19628,10 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="n">
-        <v>488</v>
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -19643,41 +19645,25 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Emprego de S vs. Z e Dígrafos</t>
+          <t>Emprego de S com som de Z</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Uso do "S" com som de "Z"&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Sufixos de Adjetivos Pátrios, Títulos ou Estado:&lt;/strong&gt; -ês, -esa, -isa.
-        &lt;ul&gt;
-          &lt;li&gt;&lt;i&gt;Ex: português, burguesia, profetisa, baronesa.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;burguezia&lt;/s&gt;, &lt;s&gt;baroneza&lt;/s&gt;).&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Derivados de Radicais com "S":&lt;/strong&gt; Mantém-se a grafia original do verbo ou substantivo base.
-        &lt;ul&gt;
-          &lt;li&gt;&lt;i&gt;Ex: pesquisa $\rightarrow$ pesquisar; improviso $\rightarrow$ improvisar; aviso $\rightarrow$ avisar.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;pesquiza&lt;/s&gt;, &lt;s&gt;improvizo&lt;/s&gt;).&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Após Ditongos:&lt;/strong&gt; Usa-se o "s" quando houver encontro vocálico precedente.
-        &lt;ul&gt;
-          &lt;li&gt;&lt;i&gt;Ex: coisa, causa, lousa, querosene.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;querozene&lt;/s&gt;).&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Dígrafos Consonantais (CH vs X)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Dígrafo "CH":&lt;/strong&gt; Letras unidas que formam um único fonema. &lt;i&gt;Ex: desfecho, chuchu, fachada, charque.&lt;/i&gt;&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Obrigatoriedade do "X":&lt;/strong&gt; 
-        &lt;ul&gt;
-          &lt;li&gt;Após ditongos (ex: &lt;i&gt;caixa, feixe&lt;/i&gt;, &lt;i&gt;coaxar&lt;/i&gt;, &lt;i&gt;deixar&lt;/i&gt;).&lt;/li&gt;
-          &lt;li&gt;Após a sílaba "me" (ex: &lt;i&gt;mexer&lt;/i&gt;, exceto em &lt;i&gt;mecha&lt;/i&gt; de cabelo).&lt;/li&gt;
-          &lt;li&gt;Após "en" (ex: &lt;i&gt;enxada, enxoval&lt;/i&gt;, exceto derivados de palavras base que já possuem CH, como &lt;i&gt;encher&lt;/i&gt;).&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Sufixos de Adjetivos Pátrios, Títulos ou Estado:&lt;/strong&gt; -ês, -esa, -isa.
+    &lt;ul&gt;
+      &lt;li&gt;&lt;i&gt;Ex: português, burguesia, profetisa, baronesa.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;burguezia&lt;/s&gt;, &lt;s&gt;baroneza&lt;/s&gt;).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Derivados de Radicais com "S":&lt;/strong&gt; Mantém-se a grafia original do verbo ou substantivo base.
+    &lt;ul&gt;
+      &lt;li&gt;&lt;i&gt;Ex: pesquisa $\rightarrow$ pesquisar; improviso $\rightarrow$ improvisar; aviso $\rightarrow$ avisar.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;pesquiza&lt;/s&gt;, &lt;s&gt;improvizo&lt;/s&gt;).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Após Ditongos:&lt;/strong&gt; Usa-se o "s" quando houver encontro vocálico precedente.
+    &lt;ul&gt;
+      &lt;li&gt;&lt;i&gt;Ex: coisa, causa, lousa, querosene.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;querozene&lt;/s&gt;).&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -21013,6 +20999,56 @@
         <v>0</v>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>510</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Ortografia e Acentuação</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>X vs CH</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Obrigatoriedade do "X"&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Após ditongos:&lt;/strong&gt; &lt;i&gt;caixa, feixe, frouxo, deixar, coaxar.&lt;/i&gt; (Exceções: &lt;i&gt;recauchutar, guache&lt;/i&gt;).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Após a sílaba inicial "me-":&lt;/strong&gt; &lt;i&gt;mexer, mexicano, mexerico.&lt;/i&gt; (Exceção única: &lt;i&gt;mecha&lt;/i&gt; de cabelo).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Após a sílaba inicial "en-":&lt;/strong&gt; &lt;i&gt;enxada, enxoval, enxaguar.&lt;/i&gt; 
+        &lt;ul&gt;
+          &lt;li&gt;&lt;b&gt;Cuidado (O truque da banca):&lt;/b&gt; Se a palavra base já tiver "CH", o derivado com "en-" mantém o "CH". &lt;i&gt;Ex: cheio $\rightarrow$ encher; charco $\rightarrow$ encharcar; chiqueiro $\rightarrow$ enchiqueirar.&lt;/i&gt;&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Origem indígena ou africana:&lt;/strong&gt; &lt;i&gt;xavante, xampu, abacaxi, xingar.&lt;/i&gt;&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Uso do "CH" (Além das exceções acima)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Derivação lógica:&lt;/strong&gt; Mantém-se o "CH" se a raiz da palavra já o contiver. &lt;i&gt;Ex: cheiro $\rightarrow$ cheirosa; inchar $\rightarrow$ inchado.&lt;/i&gt;&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Termos aportuguesados comuns:&lt;/strong&gt; &lt;i&gt;salsicha, capricho, fachada, desfecho, charque, mochila.&lt;/i&gt;&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F361" t="n">
+        <v>0</v>
+      </c>
+      <c r="G361" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G361"/>
+  <dimension ref="A1:G370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21049,6 +21049,520 @@
         <v>0</v>
       </c>
     </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>511</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Gestão Económica e Modelo GECON</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+    &lt;ul&gt;
+        &lt;li&gt;&lt;b&gt;Gestão económica&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;administração baseada em resultados económicos&lt;/li&gt;
+                &lt;li&gt;foco da avaliação de decisões
+                    &lt;ul&gt;
+                        &lt;li&gt;criação ou destruição de valor&lt;/li&gt;
+                        &lt;li&gt;comparação com a melhor alternativa disponível (custo de oportunidade)&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;Modelo GECON&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;lucro corretamente mensurado como medida de eficácia&lt;/li&gt;
+                &lt;li&gt;visão sistémica e integração&lt;/li&gt;
+                &lt;li&gt;pilares
+                    &lt;ul&gt;
+                        &lt;li&gt;modelo de gestão (crenças e valores)&lt;/li&gt;
+                        &lt;li&gt;processo de gestão (planeamento e controlo)&lt;/li&gt;
+                        &lt;li&gt;sistema de informação (mensuração pelo resultado económico)&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+    &lt;/ul&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>0</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>512</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Princípios da Engenharia Económica e EVA</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+    &lt;ul&gt;
+        &lt;li&gt;&lt;b&gt;Engenharia económica&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;comparação monetária de alternativas de investimento e operação&lt;/li&gt;
+                &lt;li&gt;princípios de decisão
+                    &lt;ul&gt;
+                        &lt;li&gt;valor do dinheiro no tempo&lt;/li&gt;
+                        &lt;li&gt;incrementalidade (apenas fluxos que mudam com a decisão importam)&lt;/li&gt;
+                        &lt;li&gt;exclusão de custos afundados (gastos irrecuperáveis não influenciam opções futuras)&lt;/li&gt;
+                        &lt;li&gt;custo de oportunidade (retorno da alternativa preterida)&lt;/li&gt;
+                        &lt;li&gt;foco no fluxo de caixa efetivo&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;EVA (Valor Económico Agregado)&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;criação de valor após remunerar o capital pelo custo de oportunidade&lt;/li&gt;
+                &lt;li&gt;fórmulas
+                    &lt;ul&gt;
+                        &lt;li&gt;EVA = Lucro operacional líquido de impostos - (Custo de capital × Capital investido)&lt;/li&gt;
+                        &lt;li&gt;EVA = Capital investido × (Retorno sobre o capital - Custo do capital)&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+    &lt;/ul&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>0</v>
+      </c>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>513</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Terminologia de Custos e Ciclo de Vida</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+    &lt;ul&gt;
+        &lt;li&gt;&lt;b&gt;Classificação de custos&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;quanto ao volume
+                    &lt;ul&gt;
+                        &lt;li&gt;fixos (não mudam com a quantidade produzida na capacidade instalada)&lt;/li&gt;
+                        &lt;li&gt;variáveis (mudam proporcionalmente)&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+                &lt;li&gt;quanto ao produto
+                    &lt;ul&gt;
+                        &lt;li&gt;diretos (mensuração objetiva)&lt;/li&gt;
+                        &lt;li&gt;indiretos (necessitam de rateio)&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;Ciclo de vida do projeto&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;implantação
+                    &lt;ul&gt;
+                        &lt;li&gt;Capex (despesas de capital e obras)&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+                &lt;li&gt;operação
+                    &lt;ul&gt;
+                        &lt;li&gt;Opex (despesas recorrentes de funcionamento)&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+                &lt;li&gt;desativação
+                    &lt;ul&gt;
+                        &lt;li&gt;custos de encerramento e descomissionamento&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+    &lt;/ul&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>0</v>
+      </c>
+      <c r="G364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>514</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Microeconomia e Ponto de Equilíbrio</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+    &lt;ul&gt;
+        &lt;li&gt;&lt;b&gt;Elasticidade-preço da procura&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;sensibilidade da quantidade à variação de preço&lt;/li&gt;
+                &lt;li&gt;Ep = 0: perfeitamente inelástica&lt;/li&gt;
+                &lt;li&gt;0 &amp;lt; Ep &amp;lt; 1: inelástica&lt;/li&gt;
+                &lt;li&gt;Ep &amp;gt; 1: elástica&lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;Teoria da produção&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;lei dos rendimentos decrescentes (acréscimos marginais sucessivamente menores)&lt;/li&gt;
+                &lt;li&gt;ponto de encerramento (quando o preço cai abaixo do custo variável médio mínimo)&lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;Ponto de Equilíbrio (Nivelamento)&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;Receita Total = Custo Total (lucro zero)&lt;/li&gt;
+                &lt;li&gt;quantidade = Custo Fixo / (Preço - Custo Variável Unitário)&lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+    &lt;/ul&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>515</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Estudo de Mercado e Procura</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+    &lt;ul&gt;
+        &lt;li&gt;&lt;b&gt;Análise de mercado&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;bens finais (consumidor direto)&lt;/li&gt;
+                &lt;li&gt;bens intermediários (procura derivada da produção do bem final)&lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;Consumo Aparente (CA)&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;CA = Produção Nacional + Importações - Exportações&lt;/li&gt;
+                &lt;li&gt;substitui a medição do consumo real por ignorar a variação de &lt;i&gt;stocks&lt;/i&gt;&lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;Projeção da procura futura&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;extrapolação de tendência histórica&lt;/li&gt;
+                &lt;li&gt;coeficientes de elasticidade
+                    &lt;ul&gt;
+                        &lt;li&gt;Mn = Mo × (1 + taxa populacional + Ey × taxa de rendimento - Ep × taxa de preço)&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+    &lt;/ul&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F366" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>516</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Engenharia de Projeto e Tecnologias</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+    &lt;ul&gt;
+        &lt;li&gt;&lt;b&gt;Etapas da engenharia&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;ensaios preliminares e provas de conceito (mitigação de risco)&lt;/li&gt;
+                &lt;li&gt;seleção de processo e equipamentos&lt;/li&gt;
+                &lt;li&gt;construção civil e &lt;i&gt;layout&lt;/i&gt; espacial&lt;/li&gt;
+                &lt;li&gt;quantificação de insumos e mão de obra&lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;Seleção tecnológica&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;processo estruturado
+                    &lt;ul&gt;
+                        &lt;li&gt;definição de requisitos&lt;/li&gt;
+                        &lt;li&gt;prospeção tecnológica para avaliar maturidade&lt;/li&gt;
+                        &lt;li&gt;filtro de viabilidade local antes do contacto com fornecedores&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+                &lt;li&gt;distorções comuns
+                    &lt;ul&gt;
+                        &lt;li&gt;"seleção por lista telefónica" (escolha simplificada sem prospeção)&lt;/li&gt;
+                        &lt;li&gt;aquisição injustificada de bens importados intensivos em capital&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+    &lt;/ul&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>517</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Investimentos e Financiamento</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+    &lt;ul&gt;
+        &lt;li&gt;&lt;b&gt;Juros durante a construção&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;integram o investimento fixo (Capex) e não os custos operacionais&lt;/li&gt;
+                &lt;li&gt;cálculo com circularidade
+                    &lt;ul&gt;
+                        &lt;li&gt;I = Soma das parcelas / (1 - percentual financiado × taxa de juros)&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;Fontes de financiamento&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;internas
+                    &lt;ul&gt;
+                        &lt;li&gt;reinversão de lucros e provisões de depreciação&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+                &lt;li&gt;externas
+                    &lt;ul&gt;
+                        &lt;li&gt;capital próprio (sócios, investidores)&lt;/li&gt;
+                        &lt;li&gt;capital de terceiros (bancos, financiamentos)&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+    &lt;/ul&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F368" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>518</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Avaliação Financeira (VPL, TIR e VAUE)</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>&lt;div&gt;
+    &lt;ul&gt;
+        &lt;li&gt;&lt;b&gt;Taxa Mínima de Atratividade (TMA)&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;custo de oportunidade do capital&lt;/li&gt;
+                &lt;li&gt;composição teórica: taxa livre de risco + prémio de risco + prémio de liquidez&lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;Valor Presente Líquido (VPL)&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;soma dos fluxos de caixa descontados à TMA deduzida do investimento&lt;/li&gt;
+                &lt;li&gt;VPL &amp;gt; 0: aceitar projeto&lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;Taxa Interna de Retorno (TIR)&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;taxa que anula o VPL&lt;/li&gt;
+                &lt;li&gt;TIR &amp;gt; TMA: aceitar projeto&lt;/li&gt;
+                &lt;li&gt;problema: múltiplas TIRs em fluxos com diversas inversões de sinal&lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+        &lt;li&gt;&lt;b&gt;Valor Anual Uniforme Equivalente (VAUE)&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;transforma o VPL numa série de parcelas uniformes ao longo da vida útil&lt;/li&gt;
+                &lt;li&gt;indicado para a comparação de projetos com horizontes temporais diferentes&lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+    &lt;/ul&gt;
+&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F369" t="n">
+        <v>0</v>
+      </c>
+      <c r="G369" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Gestão Econômica</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Indicadores Agropecuários e Agroindustriais</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+        &lt;li&gt;&lt;b&gt;Medidas de ciclo produtivo&lt;/b&gt;
+            &lt;ul&gt;
+                &lt;li&gt;Renda Líquida (RL) = Receita Total - Custo Total&lt;/li&gt;
+                &lt;li&gt;Renda da Família (RF) = RL + Custo de Oportunidade + Custo do Trabalho Familiar&lt;/li&gt;
+                &lt;li&gt;Taxa de retorno do empreendedor = RL / Custo Total&lt;/li&gt;
+            &lt;/ul&gt;
+        &lt;/li&gt;
+    &lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G370"/>
+  <dimension ref="A1:G381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21563,6 +21563,501 @@
         <v>0</v>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>520</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Internet das Coisas (IoT - Internet of Things)</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;rede de objetos físicos embarcados com sensores, &lt;i&gt;software&lt;/i&gt; e conectividade&lt;/li&gt;
+            &lt;li&gt;permite a comunicação e a troca de dados em tempo real entre máquinas e sistemas&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;monitoramento contínuo do chão de fábrica&lt;/li&gt;
+            &lt;li&gt;rastreabilidade completa de ativos e materiais&lt;/li&gt;
+            &lt;li&gt;base para a manutenção preditiva&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>521</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Sistemas Ciberfísicos (CPS - Cyber-Physical Systems)</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;integração de processos computacionais e físicos&lt;/li&gt;
+            &lt;li&gt;computadores e redes monitoram e controlam os processos físicos com &lt;i&gt;loops&lt;/i&gt; de &lt;i&gt;feedback&lt;/i&gt;&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;criação de fábricas inteligentes (&lt;i&gt;smart factories&lt;/i&gt;)&lt;/li&gt;
+            &lt;li&gt;descentralização da tomada de decisão&lt;/li&gt;
+            &lt;li&gt;adaptação autônoma das máquinas a mudanças nas condições de operação&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F372" t="n">
+        <v>0</v>
+      </c>
+      <c r="G372" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>522</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Computação em Nuvem (Cloud Computing)</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;fornecimento de serviços de computação via internet&lt;/li&gt;
+            &lt;li&gt;inclui servidores, armazenamento, bancos de dados, redes e &lt;i&gt;software&lt;/i&gt;&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;redução de custos com infraestrutura local de TI (Tecnologia da Informação)&lt;/li&gt;
+            &lt;li&gt;escalabilidade rápida de armazenamento e processamento&lt;/li&gt;
+            &lt;li&gt;acesso remoto e centralizado a dados de múltiplas plantas industriais&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>523</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Big Data e Analytics (Megadados e Análise de Dados)</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;coleta e análise de conjuntos de dados massivos e complexos&lt;/li&gt;
+            &lt;li&gt;extração de valor e padrões a partir do volume, velocidade e variedade de informações&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;otimização da qualidade da produção em tempo real&lt;/li&gt;
+            &lt;li&gt;identificação de gargalos operacionais invisíveis a análises tradicionais&lt;/li&gt;
+            &lt;li&gt;previsão de demanda com maior precisão e ajuste de capacidade produtiva&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F374" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>524</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Simulação e Gêmeos Digitais (Digital Twins)</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;réplica virtual exata de um produto, processo ou sistema físico&lt;/li&gt;
+            &lt;li&gt;alimentada com dados em tempo real via IoT&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;testes e otimizações de &lt;i&gt;layout&lt;/i&gt; e processos sem interrupção da linha física&lt;/li&gt;
+            &lt;li&gt;redução do tempo e custo de comissionamento de novos equipamentos&lt;/li&gt;
+            &lt;li&gt;simulação de cenários de falha para treinamento e mitigação de riscos&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>525</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Manufatura Aditiva (Impressão 3D)</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;criação de objetos tridimensionais a partir de modelos digitais&lt;/li&gt;
+            &lt;li&gt;adição sucessiva de camadas de material (plástico, metal, resina)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;prototipagem rápida e barateamento do desenvolvimento de produtos&lt;/li&gt;
+            &lt;li&gt;produção de lotes unitários ou peças de reposição sob demanda&lt;/li&gt;
+            &lt;li&gt;redução drástica de perdas e resíduos de matéria-prima comparada à usinagem tradicional&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>526</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Robótica Autônoma</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;robôs industriais com inteligência artificial para agir sem intervenção humana direta&lt;/li&gt;
+            &lt;li&gt;inclui robôs colaborativos (&lt;i&gt;cobots&lt;/i&gt;) que interagem de forma segura com operadores&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;assunção de tarefas repetitivas, insalubres ou de alta precisão&lt;/li&gt;
+            &lt;li&gt;aumento da flexibilidade da linha de montagem&lt;/li&gt;
+            &lt;li&gt;redução de acidentes de trabalho e de custos operacionais de longo prazo&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>0</v>
+      </c>
+      <c r="G377" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>527</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Segurança Cibernética (Cybersecurity)</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;proteção de sistemas, redes e programas contra ataques digitais&lt;/li&gt;
+            &lt;li&gt;garantia de integridade, confidencialidade e disponibilidade dos dados&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;proteção de dados industriais sensíveis e propriedade intelectual&lt;/li&gt;
+            &lt;li&gt;prevenção contra paralisações de fábrica causadas por &lt;i&gt;ransomware&lt;/i&gt; (&lt;i&gt;software&lt;/i&gt; de extorsão)&lt;/li&gt;
+            &lt;li&gt;garantia de operação contínua e segura dos sistemas ciberfísicos e maquinários&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>0</v>
+      </c>
+      <c r="G378" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>528</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Integração de Sistemas (Horizontal e Vertical)</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Horizontal: integração de dados entre fornecedores, empresa e clientes ao longo da cadeia de valor&lt;/li&gt;
+            &lt;li&gt;Vertical: integração de dados entre os diferentes níveis hierárquicos da empresa (do chão de fábrica ao ERP corporativo - &lt;i&gt;Enterprise Resource Planning&lt;/i&gt; / Planejamento de Recursos Empresariais)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;fluxo de informações contínuo e sem silos departamentais&lt;/li&gt;
+            &lt;li&gt;agilidade na resposta a atrasos de fornecimento ou picos de demanda&lt;/li&gt;
+            &lt;li&gt;alinhamento total entre a execução física e o planejamento estratégico&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>0</v>
+      </c>
+      <c r="G379" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>529</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Inteligência Artificial (IA - Artificial Intelligence)</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;simulação de capacidades cognitivas humanas por sistemas computacionais&lt;/li&gt;
+            &lt;li&gt;engloba raciocínio, resolução de problemas, perceção e tomada de decisão&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;orquestração inteligente e autónoma de toda a cadeia de suprimentos&lt;/li&gt;
+            &lt;li&gt;sistemas de visão computacional avançada para inspeção de qualidade&lt;/li&gt;
+            &lt;li&gt;otimização instantânea de rotas, consumo energético e alocação de recursos&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>0</v>
+      </c>
+      <c r="G380" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>530</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Machine Learning (ML) / Aprendizado de Máquina</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;subcampo da IA focado em algoritmos que aprendem empiricamente com os dados&lt;/li&gt;
+            &lt;li&gt;permite que os sistemas melhorem o seu desempenho sem programação explícita para cada nova situação&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;coração da manutenção preditiva, cruzando dados históricos para prever falhas antes que ocorram&lt;/li&gt;
+            &lt;li&gt;identificação de padrões ocultos e anomalias em grandes volumes de informação gerados pelo &lt;i&gt;Big Data&lt;/i&gt;&lt;/li&gt;
+            &lt;li&gt;ajuste autónomo e contínuo de parâmetros de maquinário para maximizar o rendimento e minimizar perdas&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>0</v>
+      </c>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G381"/>
+  <dimension ref="A1:G390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13569,8 +13569,10 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="n">
-        <v>349</v>
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -13592,6 +13594,11 @@
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito do QFD (Quality Function Deployment)&lt;/strong&gt;
     &lt;ul&gt;
+&lt;li&gt;&lt;strong&gt;Contexto e Origem&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Técnica desenvolvida no Japão e usada amplamente pela Toyota para assegurar que o projeto final atenda rigorosamente às necessidades dos clientes.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
       &lt;li&gt;Ferramenta para traduzir a "Voz do Cliente" em especificações técnicas.&lt;/li&gt;
       &lt;li&gt;Reduz mudanças de projeto de última hora e aumenta a satisfação.&lt;/li&gt;
     &lt;/ul&gt;
@@ -14649,7 +14656,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Gestão da Tecnologia</t>
+          <t>Indústria 4.0</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -14662,23 +14669,23 @@
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Pilares de Processamento e Dados&lt;/strong&gt;
     &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;1. Big Data e Analytics:&lt;/strong&gt; Coleta e avaliação massiva de dados para identificar falhas e otimizar a produção em tempo real.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;2. Computação na Nuvem (Cloud Computing):&lt;/strong&gt; Infraestrutura que permite o acesso e o compartilhamento de dados entre diferentes locais e sistemas.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;3. Cibersegurança (Cybersecurity):&lt;/strong&gt; Proteção de sistemas industriais e linhas de produção contra ameaças e invasões digitais.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;1. Big Data e Analytics:&lt;/strong&gt;&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;2. Computação na Nuvem (Cloud Computing):&lt;/strong&gt; &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;3. Cibersegurança (Cybersecurity):&lt;/strong&gt; &lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;&lt;strong&gt;Pilares de Integração e Simulação&lt;/strong&gt;
     &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;4. Integração de Sistemas (Vertical e Horizontal):&lt;/strong&gt; Conexão de todos os elos da cadeia de valor (fornecedores aos clientes) e dos níveis da fábrica (chão de fábrica à gestão).&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;5. Simulação (Digital Twins):&lt;/strong&gt; Uso de modelos virtuais para espelhar o mundo físico em simulações 3D, permitindo testes antes da execução real.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;6. Internet das Coisas (IoT):&lt;/strong&gt; Rede de objetos físicos com sensores e conectividade para trocar dados entre si e com o centro de controle.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;4. Integração de Sistemas (Vertical e Horizontal):&lt;/strong&gt;&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;5. Simulação (Digital Twins):&lt;/strong&gt;&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;6. Internet das Coisas (IoT):&lt;/strong&gt;&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;&lt;strong&gt;Pilares de Execução Física&lt;/strong&gt;
     &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;7. Robôs Autônomos:&lt;/strong&gt; Máquinas que interagem entre si, trabalham lado a lado com humanos e aprendem com novas tarefas.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;8. Manufatura Aditiva:&lt;/strong&gt; Produção de peças via impressão 3D, reduzindo estoques de peças complexas e facilitando prototipagem rápida.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;9. Realidade Aumentada (AR):&lt;/strong&gt; Sistemas que sobrepõem informações digitais ao campo de visão real (ex: instruções de manutenção projetadas em uma peça).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;7. Robôs Autônomos:&lt;/strong&gt;&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;8. Manufatura Aditiva:&lt;/strong&gt;&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;9. Realidade Aumentada (AR):&lt;/strong&gt;&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -17290,7 +17297,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -17299,48 +17306,15 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Gestão da Tecnologia</t>
+          <t>Gestão de Pessoas</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Indústria 4.0</t>
+          <t>Gestão de Pessoas por Competências</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;Máquinas realizam o trabalho de forma autônoma&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F296" t="n">
-        <v>0</v>
-      </c>
-      <c r="G296" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
-        <v>445</v>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>Gestão de Pessoas</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>Gestão de Pessoas por Competências</t>
-        </is>
-      </c>
-      <c r="E297" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Modelo gerencial que foca em identificar, gerenciar e desenvolver o CHA dos colaboradores:
@@ -17361,35 +17335,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F297" t="n">
-        <v>0</v>
-      </c>
-      <c r="G297" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
         <is>
           <t>446</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr">
+      <c r="D297" t="inlineStr">
         <is>
           <t>Kanban</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
+      <c r="E297" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Baseado em um sistema puxado
@@ -17443,33 +17417,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F298" t="n">
-        <v>0</v>
-      </c>
-      <c r="G298" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
+      <c r="F297" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
         <v>447</v>
       </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
         <is>
           <t>Gestão de Pessoas</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr">
+      <c r="D298" t="inlineStr">
         <is>
           <t>Teorias e Modelos de Liderança</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr">
+      <c r="E298" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
   &lt;li&gt;&lt;strong&gt;Teorias dos Traços de Personalidade (A abordagem mais antiga):&lt;/strong&gt;
@@ -17548,33 +17522,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F299" t="n">
-        <v>0</v>
-      </c>
-      <c r="G299" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="n">
+      <c r="F298" t="n">
+        <v>0</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
         <v>448</v>
       </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
         <is>
           <t>Gestão de Pessoas</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr">
+      <c r="D299" t="inlineStr">
         <is>
           <t>Teoria dos Dois Fatores de Herzberg</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr">
+      <c r="E299" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Fatores Higiênicos (Extrínsecos):&lt;/strong&gt;
@@ -17593,6 +17567,67 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>449</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Gestão de Pessoas</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Hierarquia das Necessidades de Maslow</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Fisiológicas (Base):&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Exigências vitais:
+        &lt;ul&gt;
+          &lt;li&gt;Alimentação, água, abrigo, descanso&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;De Segurança:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Busca por proteção, ordem, estabilidade e ausência de ameaças&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Sociais:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Interação humana, aceitação, pertencimento e amizade&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;De Estima:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Reconhecimento e valorização externa e respeito próprio&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;De Autorrealização (Topo):&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;O impulso do indivíduo de maximizar o próprio potencial, envolvendo autonomia, criatividade, superação de limites e desenvolvimento contínuo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F300" t="n">
         <v>0</v>
       </c>
@@ -17602,7 +17637,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -17616,41 +17651,14 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Hierarquia das Necessidades de Maslow</t>
+          <t>Dissonância Cognitiva</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Fisiológicas (Base):&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Exigências vitais:
-        &lt;ul&gt;
-          &lt;li&gt;Alimentação, água, abrigo, descanso&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;De Segurança:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Busca por proteção, ordem, estabilidade e ausência de ameaças&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Sociais:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Interação humana, aceitação, pertencimento e amizade&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;De Estima:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Reconhecimento e valorização externa e respeito próprio&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;De Autorrealização (Topo):&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;O impulso do indivíduo de maximizar o próprio potencial, envolvendo autonomia, criatividade, superação de limites e desenvolvimento contínuo&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
+  &lt;li&gt;Inconsistência percebida por um funcionário entre suas crenças, sentimentos e ações em relação à empresa.&lt;/li&gt;
+  &lt;li&gt;Demonstra que não apenas as emoções e atitudes levam ao comportamento, mas o oposto também pode ocorrer.&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -17663,7 +17671,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -17677,14 +17685,13 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Dissonância Cognitiva</t>
+          <t>Racionalização Excessiva</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;Inconsistência percebida por um funcionário entre suas crenças, sentimentos e ações em relação à empresa.&lt;/li&gt;
-  &lt;li&gt;Demonstra que não apenas as emoções e atitudes levam ao comportamento, mas o oposto também pode ocorrer.&lt;/li&gt;
+  &lt;li&gt;Mecanismo de defesa psicológico (tentativa de justificar comportamentos inaceitáveis com motivos lógicos).&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -17697,7 +17704,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -17711,13 +17718,28 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Racionalização Excessiva</t>
+          <t>Teoria das Necessidades Aprendidas (David McClelland)</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;Mecanismo de defesa psicológico (tentativa de justificar comportamentos inaceitáveis com motivos lógicos).&lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Necessidade de Afiliação:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Busca contínua por aceitação social, amizade e forte aversão a atritos interpessoais.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Baixa:&lt;/strong&gt; Cargos gerenciais ou posições que exigem alocação de recursos escassos.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Necessidade de Poder:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Desejo de exercer influência, controle e impacto sobre outras pessoas e sobre o ambiente organizacional.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Necessidade de Realização:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Impulso interno para alcançar a excelência, assumir responsabilidades diretas na resolução de problemas e atingir metas desafiadoras, preferência por riscos moderados e necessidade de feedback constante.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -17730,7 +17752,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -17744,58 +17766,10 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Teoria das Necessidades Aprendidas (David McClelland)</t>
+          <t>Teoria da Expectativa (Victor Vroom)</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Necessidade de Afiliação:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Busca contínua por aceitação social, amizade e forte aversão a atritos interpessoais.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Baixa:&lt;/strong&gt; Cargos gerenciais ou posições que exigem alocação de recursos escassos.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Necessidade de Poder:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Desejo de exercer influência, controle e impacto sobre outras pessoas e sobre o ambiente organizacional.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Necessidade de Realização:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Impulso interno para alcançar a excelência, assumir responsabilidades diretas na resolução de problemas e atingir metas desafiadoras, preferência por riscos moderados e necessidade de feedback constante.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F304" t="n">
-        <v>0</v>
-      </c>
-      <c r="G304" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="n">
-        <v>453</v>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>Gestão de Pessoas</t>
-        </is>
-      </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>Teoria da Expectativa (Victor Vroom)</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Expectância (Expectativa):&lt;/strong&gt; Crença de que o esforço individual dedicado à tarefa resultará no nível de desempenho desejado.&lt;/li&gt;
@@ -17804,33 +17778,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F305" t="n">
-        <v>0</v>
-      </c>
-      <c r="G305" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="n">
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
         <v>454</v>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
         <is>
           <t>Gestão de Pessoas</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr">
+      <c r="D305" t="inlineStr">
         <is>
           <t>Teoria da Equidade (J. Stacy Adams)</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
+      <c r="E305" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Percepção de Justiça&lt;/li&gt;
@@ -17850,33 +17824,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F306" t="n">
-        <v>0</v>
-      </c>
-      <c r="G306" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="n">
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
         <v>455</v>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
         <is>
           <t>Gestão de Pessoas</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr">
+      <c r="D306" t="inlineStr">
         <is>
           <t>Teoria do Caminho-Objetivo (Robert House)</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
+      <c r="E306" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Estabelece que cada estilo de liderança relaciona-se com variáveis situacionais.&lt;/li&gt;
@@ -17923,33 +17897,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F307" t="n">
-        <v>0</v>
-      </c>
-      <c r="G307" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="n">
+      <c r="F306" t="n">
+        <v>0</v>
+      </c>
+      <c r="G306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
         <v>456</v>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
         <is>
           <t>Gestão de Pessoas</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr">
+      <c r="D307" t="inlineStr">
         <is>
           <t>Liderança Transacional vs Transformacional (Bass e Burns)</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
+      <c r="E307" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Líder Transacional:&lt;/strong&gt;
@@ -17978,33 +17952,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F308" t="n">
-        <v>0</v>
-      </c>
-      <c r="G308" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="n">
+      <c r="F307" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
         <v>457</v>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr">
+      <c r="D308" t="inlineStr">
         <is>
           <t>Protocolos de Avaliação Ergonômica</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
+      <c r="E308" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;strong&gt;Método OCRA (Occupational Repetitive Actions)&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
@@ -18050,6 +18024,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>458</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Ergonomia (NR17): Transporte Manual de Cargas</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Limites de Peso para Mulheres e Menores (Art. 390 da CLT):
+    &lt;ul&gt;
+      &lt;li&gt;Trabalho contínuo: Máximo 20 kg&lt;/li&gt;
+      &lt;li&gt;Trabalho ocasional: Máximo 25 kg&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Limitação para Homens Adultos (Art. 198 da CLT):
+    &lt;ul&gt;
+      &lt;li&gt;Máximo 60 kg&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;A NR17 exige que o peso não comprometa a saúde ou a segurança do trabalhador, independente desse limite.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F309" t="n">
         <v>0</v>
       </c>
@@ -18059,7 +18077,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -18073,24 +18091,30 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Ergonomia (NR17): Transporte Manual de Cargas</t>
+          <t>Áreas da Ergonomia</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;Limites de Peso para Mulheres e Menores (Art. 390 da CLT):
-    &lt;ul&gt;
-      &lt;li&gt;Trabalho contínuo: Máximo 20 kg&lt;/li&gt;
-      &lt;li&gt;Trabalho ocasional: Máximo 25 kg&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;Limitação para Homens Adultos (Art. 198 da CLT):
-    &lt;ul&gt;
-      &lt;li&gt;Máximo 60 kg&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;A NR17 exige que o peso não comprometa a saúde ou a segurança do trabalhador, independente desse limite.&lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Ergonomia Física:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Conforto no ambiente de trabalho e na prevenção de lesões musculoesqueléticas&lt;/li&gt;
+      &lt;li&gt;Características anatômicas, antropométricas, fisiológicas e biomecânicas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Ergonomia Organizacional:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Otimização dos sistemas sociotécnicos&lt;/li&gt;
+      &lt;li&gt;Estruturas organizacionais, políticas e processos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Ergonomia Cognitiva:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Processos mentais&lt;/li&gt;
+      &lt;li&gt;Percepção, memória, raciocínio e resposta motora&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -18103,7 +18127,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -18117,60 +18141,10 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Áreas da Ergonomia</t>
+          <t>Análise Ergonômica do Trabalho (AET)</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Ergonomia Física:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Conforto no ambiente de trabalho e na prevenção de lesões musculoesqueléticas&lt;/li&gt;
-      &lt;li&gt;Características anatômicas, antropométricas, fisiológicas e biomecânicas&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Ergonomia Organizacional:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Otimização dos sistemas sociotécnicos&lt;/li&gt;
-      &lt;li&gt;Estruturas organizacionais, políticas e processos&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Ergonomia Cognitiva:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Processos mentais&lt;/li&gt;
-      &lt;li&gt;Percepção, memória, raciocínio e resposta motora&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F311" t="n">
-        <v>0</v>
-      </c>
-      <c r="G311" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="n">
-        <v>460</v>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>Análise Ergonômica do Trabalho (AET)</t>
-        </is>
-      </c>
-      <c r="E312" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Estudo técnico, aprofundado e sistemático das condições de trabalho&lt;/li&gt;
@@ -18205,6 +18179,54 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F311" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>461</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Adaptação do Mobiliário e Apoio para os Pés</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;O mobiliário dos postos de trabalho deve ser concebido e adaptado para atender às características psicofisiológicas dos trabalhadores e às suas dimensões antropométricas&lt;/li&gt;
+  &lt;li&gt;Regras sobre o uso do Apoio para os Pés:
+    &lt;ul&gt;
+      &lt;li&gt;Condição de fornecimento:
+        &lt;ul&gt;
+          &lt;li&gt;Não é uma exigência obrigatória para todos os postos de trabalho sentados de forma indiscriminada.&lt;/li&gt;
+          &lt;li&gt;Deve ser utilizado sempre que o trabalhador não conseguir manter a região plantar dos pés completamente apoiada no piso.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Finalidade:
+        &lt;ul&gt;
+          &lt;li&gt;Serve para a adaptação do posto de trabalho ao biotipo do trabalhador&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F312" t="n">
         <v>0</v>
       </c>
@@ -18214,7 +18236,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -18228,58 +18250,10 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Adaptação do Mobiliário e Apoio para os Pés</t>
+          <t>NR17 (Anexo I) - Operadores de Checkout</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;O mobiliário dos postos de trabalho deve ser concebido e adaptado para atender às características psicofisiológicas dos trabalhadores e às suas dimensões antropométricas&lt;/li&gt;
-  &lt;li&gt;Regras sobre o uso do Apoio para os Pés:
-    &lt;ul&gt;
-      &lt;li&gt;Condição de fornecimento:
-        &lt;ul&gt;
-          &lt;li&gt;Não é uma exigência obrigatória para todos os postos de trabalho sentados de forma indiscriminada.&lt;/li&gt;
-          &lt;li&gt;Deve ser utilizado sempre que o trabalhador não conseguir manter a região plantar dos pés completamente apoiada no piso.&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;Finalidade:
-        &lt;ul&gt;
-          &lt;li&gt;Serve para a adaptação do posto de trabalho ao biotipo do trabalhador&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F313" t="n">
-        <v>0</v>
-      </c>
-      <c r="G313" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="n">
-        <v>462</v>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>NR17 (Anexo I) - Operadores de Checkout</t>
-        </is>
-      </c>
-      <c r="E314" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;strong&gt;Posto de Trabalho e Mobiliário&lt;/strong&gt;&lt;/p&gt;
 &lt;ul&gt;
@@ -18330,33 +18304,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F314" t="n">
-        <v>0</v>
-      </c>
-      <c r="G314" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="n">
+      <c r="F313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
         <v>463</v>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
+      <c r="D314" t="inlineStr">
         <is>
           <t>Normas Regulamentadoras (Todas as NRs)</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
+      <c r="E314" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
   &lt;li&gt;Disposições Gerais e Gerenciamento de Riscos Ocupacionais&lt;/li&gt;
@@ -18400,33 +18374,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F315" t="n">
-        <v>0</v>
-      </c>
-      <c r="G315" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="n">
+      <c r="F314" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
         <v>464</v>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
+      <c r="D315" t="inlineStr">
         <is>
           <t>NR33 - Segurança e Saúde nos Trabalhos em Espaços Confinados</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
+      <c r="E315" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Espaço Confinado:&lt;/strong&gt; qualquer área não projetada para ocupação humana contínua, com meios limitados de entrada e saída, e com ventilação insuficiente para remover contaminantes ou onde possa existir deficiência/enriquecimento de oxigênio&lt;/li&gt;
@@ -18454,33 +18428,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F316" t="n">
-        <v>0</v>
-      </c>
-      <c r="G316" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="n">
+      <c r="F315" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
         <v>465</v>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
+      <c r="D316" t="inlineStr">
         <is>
           <t>NR35 - Trabalho em Altura</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr">
+      <c r="E316" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Acima de 2 m do nível inferior&lt;/li&gt;
@@ -18518,35 +18492,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F317" t="n">
-        <v>0</v>
-      </c>
-      <c r="G317" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
+      <c r="F316" t="n">
+        <v>0</v>
+      </c>
+      <c r="G316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
         <is>
           <t>467</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
+      <c r="C317" t="inlineStr">
         <is>
           <t>Concordância Verbal e Nominal</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
+      <c r="D317" t="inlineStr">
         <is>
           <t>Sujeito Partitivo (Conceito e Concordância Verbal)</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr">
+      <c r="E317" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;A Estrutura do Sujeito Partitivo&lt;/strong&gt;
@@ -18577,33 +18551,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F318" t="n">
-        <v>0</v>
-      </c>
-      <c r="G318" t="n">
+      <c r="F317" t="n">
+        <v>0</v>
+      </c>
+      <c r="G317" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="n">
+    <row r="318">
+      <c r="A318" t="n">
         <v>468</v>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>Estatística</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
+      <c r="C318" t="inlineStr">
         <is>
           <t>Probabilidade</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr">
+      <c r="D318" t="inlineStr">
         <is>
           <t>Probabilidade Condicional</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr">
+      <c r="E318" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Definição: probabilidade de ocorrência de um evento $A$, dado que o evento $B$ já ocorreu&lt;/li&gt;
@@ -18639,33 +18613,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F319" t="n">
-        <v>0</v>
-      </c>
-      <c r="G319" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="n">
+      <c r="F318" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
         <v>469</v>
       </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr">
+      <c r="D319" t="inlineStr">
         <is>
           <t>Curva de Phillips (Curto e Longo Prazo)</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr">
+      <c r="E319" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;strong&gt;Conceito Central&lt;/strong&gt;
@@ -18690,35 +18664,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F320" t="n">
-        <v>0</v>
-      </c>
-      <c r="G320" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
+      <c r="F319" t="n">
+        <v>0</v>
+      </c>
+      <c r="G319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
         <is>
           <t>470</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr">
+      <c r="D320" t="inlineStr">
         <is>
           <t>Elasticidade-Preço da Demanda (EPD)</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr">
+      <c r="E320" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;strong&gt;Definição&lt;/strong&gt;
@@ -18746,33 +18720,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F321" t="n">
-        <v>0</v>
-      </c>
-      <c r="G321" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="n">
+      <c r="F320" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
         <v>471</v>
       </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr">
+      <c r="D321" t="inlineStr">
         <is>
           <t>Índices de Inflação: IPC vs. Deflator do PIB</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr">
+      <c r="E321" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;strong&gt;Índice de Preços ao Consumidor (IPC)&lt;/strong&gt;
@@ -18792,33 +18766,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F322" t="n">
-        <v>0</v>
-      </c>
-      <c r="G322" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="n">
+      <c r="F321" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
         <v>472</v>
       </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr">
+      <c r="D322" t="inlineStr">
         <is>
           <t>Economias e Deseconomias de Escala</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr">
+      <c r="E322" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;strong&gt;Economia de Escala&lt;/strong&gt;
@@ -18842,33 +18816,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F323" t="n">
-        <v>0</v>
-      </c>
-      <c r="G323" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="n">
+      <c r="F322" t="n">
+        <v>0</v>
+      </c>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
         <v>473</v>
       </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr">
+      <c r="D323" t="inlineStr">
         <is>
           <t>Alavancagem Operacional e Financeira</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr">
+      <c r="E323" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;strong&gt;Alavancagem Operacional&lt;/strong&gt;
@@ -18897,35 +18871,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F324" t="n">
-        <v>0</v>
-      </c>
-      <c r="G324" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
+      <c r="F323" t="n">
+        <v>0</v>
+      </c>
+      <c r="G323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
         <is>
           <t>474</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B324" t="inlineStr">
         <is>
           <t>Matemática Financeira</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
+      <c r="C324" t="inlineStr">
         <is>
           <t>Operações de Desconto</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr">
+      <c r="D324" t="inlineStr">
         <is>
           <t>Operações de Desconto: Teoria e Relações Conceituais</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr">
+      <c r="E324" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceitos Iniciais&lt;/strong&gt;
@@ -18955,6 +18929,57 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F324" t="n">
+        <v>0</v>
+      </c>
+      <c r="G324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Operações de Desconto</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Fórmulas de Desconto Simples</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Desconto Racional Simples (Por Dentro)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Fórmula do Desconto:&lt;/strong&gt; $D_{RS}=A \times i \times t$[cite: 6, 25].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=\frac{N}{(1+i \times t)}$[cite: 6, 25].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Desconto Comercial Simples (Por Fora)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Fórmula do Desconto:&lt;/strong&gt; $D_{CS}=N \times i \times t$[cite: 7, 25].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=N \times (1-i \times t)$[cite: 7, 25].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Relação Matemática entre os Descontos Simples&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;conhecendo um dos descontos, pode obter-se o outro através da expressão: $D_{CS}=D_{RS} \times (1+i \times t)$[cite: 11, 25].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F325" t="n">
         <v>0</v>
       </c>
@@ -18965,7 +18990,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -18980,27 +19005,22 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Fórmulas de Desconto Simples</t>
+          <t>Fórmulas de Desconto Composto</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Desconto Racional Simples (Por Dentro)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Fórmula do Desconto:&lt;/strong&gt; $D_{RS}=A \times i \times t$[cite: 6, 25].&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=\frac{N}{(1+i \times t)}$[cite: 6, 25].&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Desconto Comercial Simples (Por Fora)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Fórmula do Desconto:&lt;/strong&gt; $D_{CS}=N \times i \times t$[cite: 7, 25].&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=N \times (1-i \times t)$[cite: 7, 25].&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Relação Matemática entre os Descontos Simples&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;conhecendo um dos descontos, pode obter-se o outro através da expressão: $D_{CS}=D_{RS} \times (1+i \times t)$[cite: 11, 25].&lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Desconto Racional Composto (Por Dentro)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=\frac{N}{(1+i)^t}$[cite: 14, 25].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Cálculo do Desconto:&lt;/strong&gt; $D_{RC}=N-A$[cite: 14, 25].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Desconto Comercial Composto (Por Fora)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=N \times (1-i)^t$[cite: 14, 25].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Cálculo do Desconto:&lt;/strong&gt; $D_{CC}=N-A$[cite: 14, 25].&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -19016,7 +19036,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>478</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -19026,61 +19046,15 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Operações de Desconto</t>
+          <t>Equivalência de Capitais</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Fórmulas de Desconto Composto</t>
+          <t>Equivalência de Capitais e Deslocamento no Tempo</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Desconto Racional Composto (Por Dentro)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=\frac{N}{(1+i)^t}$[cite: 14, 25].&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Cálculo do Desconto:&lt;/strong&gt; $D_{RC}=N-A$[cite: 14, 25].&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Desconto Comercial Composto (Por Fora)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Valor Atual:&lt;/strong&gt; $A=N \times (1-i)^t$[cite: 14, 25].&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Cálculo do Desconto:&lt;/strong&gt; $D_{CC}=N-A$[cite: 14, 25].&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F327" t="n">
-        <v>0</v>
-      </c>
-      <c r="G327" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>478</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Equivalência de Capitais</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>Equivalência de Capitais e Deslocamento no Tempo</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito Base&lt;/strong&gt;
@@ -19102,6 +19076,53 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F327" t="n">
+        <v>0</v>
+      </c>
+      <c r="G327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>479</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Operações de Desconto</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Taxa Efetiva em Operações de Desconto</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito de Taxa Efetiva&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;é a taxa de juros que, ao ser aplicada sobre o Valor Atual, gera o Valor Nominal no período considerado[cite: 18, 23].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Característica do Desconto Comercial&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;a taxa de desconto comercial &lt;strong&gt;não é&lt;/strong&gt; uma taxa efetiva, dado que incide sobre o Valor Nominal[cite: 19, 24].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Fórmula de Conversão (Desconto Comercial Simples)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;$i_{ef}=\frac{i_{cs}}{1-i_{cs} \times t}$[cite: 18, 25].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F328" t="n">
         <v>0</v>
       </c>
@@ -19111,7 +19132,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -19120,30 +19141,32 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Operações de Desconto</t>
+          <t>Equivalência de Capitais</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Taxa Efetiva em Operações de Desconto</t>
+          <t>Rendas Uniformes (Séries de Pagamento): Valor Atual (VA)</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Conceito de Taxa Efetiva&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;é a taxa de juros que, ao ser aplicada sobre o Valor Atual, gera o Valor Nominal no período considerado[cite: 18, 23].&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Característica do Desconto Comercial&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;a taxa de desconto comercial &lt;strong&gt;não é&lt;/strong&gt; uma taxa efetiva, dado que incide sobre o Valor Nominal[cite: 19, 24].&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Fórmula de Conversão (Desconto Comercial Simples)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;$i_{ef}=\frac{i_{cs}}{1-i_{cs} \times t}$[cite: 18, 25].&lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito de Rendas Uniformes (Certas)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;sequência de fluxos de caixa em intervalos de tempo iguais, com parcelas constantes[cite: 70, 88].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Valor Atual de Rendas Postecipadas (Fim do período)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;$VA=P \times \left[ \frac{(1+i)^n-1}{i \times (1+i)^n} \right]$ ou $VA=P \times \left[ \frac{1-(1+i)^{-n}}{i} \right]$[cite: 71, 88].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Fator de Valor Atual:&lt;/strong&gt; $a_{n-i}=\left[ \frac{(1+i)^n-1}{i \times (1+i)^n} \right]$[cite: 73, 88]. O Fator de Recuperação de Capital (FRC) é o seu inverso: $FRC=\frac{1}{a_{n-i}}$[cite: 73, 88].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Valor Atual de Rendas Antecipadas (Início do período)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;a fórmula é idêntica à das rendas postecipadas, sendo no final multiplicada pelo fator de capitalização $(1+i)$[cite: 77, 88].&lt;/li&gt;
+      &lt;li&gt;$VA=P \times \left[ \frac{(1+i)^n-1}{i \times (1+i)^n} \right] \times (1+i)$[cite: 77].&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -19158,7 +19181,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -19172,27 +19195,22 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Rendas Uniformes (Séries de Pagamento): Valor Atual (VA)</t>
+          <t>Rendas Uniformes (Séries de Pagamento): Valor Futuro (VF)</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Conceito de Rendas Uniformes (Certas)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;sequência de fluxos de caixa em intervalos de tempo iguais, com parcelas constantes[cite: 70, 88].&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Valor Atual de Rendas Postecipadas (Fim do período)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;$VA=P \times \left[ \frac{(1+i)^n-1}{i \times (1+i)^n} \right]$ ou $VA=P \times \left[ \frac{1-(1+i)^{-n}}{i} \right]$[cite: 71, 88].&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Fator de Valor Atual:&lt;/strong&gt; $a_{n-i}=\left[ \frac{(1+i)^n-1}{i \times (1+i)^n} \right]$[cite: 73, 88]. O Fator de Recuperação de Capital (FRC) é o seu inverso: $FRC=\frac{1}{a_{n-i}}$[cite: 73, 88].&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Valor Atual de Rendas Antecipadas (Início do período)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;a fórmula é idêntica à das rendas postecipadas, sendo no final multiplicada pelo fator de capitalização $(1+i)$[cite: 77, 88].&lt;/li&gt;
-      &lt;li&gt;$VA=P \times \left[ \frac{(1+i)^n-1}{i \times (1+i)^n} \right] \times (1+i)$[cite: 77].&lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Valor Futuro de Rendas Postecipadas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;$VF=P \times \left[ \frac{(1+i)^n-1}{i} \right]$[cite: 74, 88].&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Fator de Valor Futuro (Acumulação):&lt;/strong&gt; $S_{n-i}=\left[ \frac{(1+i)^n-1}{i} \right]$[cite: 76, 89]. O Fator de Formação de Capital (FFC) é o seu inverso: $FFC=\frac{1}{S_{n-i}}$[cite: 76, 89].&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Valor Futuro de Rendas Antecipadas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;a expressão matemática do Valor Futuro para uma série antecipada é &lt;strong&gt;igual&lt;/strong&gt; à da série postecipada[cite: 78].&lt;/li&gt;
+      &lt;li&gt;a multiplicação adicional pelo fator $(1+i)$ verifica-se apenas no cálculo do Valor Atual[cite: 78].&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -19207,7 +19225,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -19221,54 +19239,10 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Rendas Uniformes (Séries de Pagamento): Valor Futuro (VF)</t>
+          <t>Rendas Perpétuas (Termos Ilimitados)</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Valor Futuro de Rendas Postecipadas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;$VF=P \times \left[ \frac{(1+i)^n-1}{i} \right]$[cite: 74, 88].&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Fator de Valor Futuro (Acumulação):&lt;/strong&gt; $S_{n-i}=\left[ \frac{(1+i)^n-1}{i} \right]$[cite: 76, 89]. O Fator de Formação de Capital (FFC) é o seu inverso: $FFC=\frac{1}{S_{n-i}}$[cite: 76, 89].&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Valor Futuro de Rendas Antecipadas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;a expressão matemática do Valor Futuro para uma série antecipada é &lt;strong&gt;igual&lt;/strong&gt; à da série postecipada[cite: 78].&lt;/li&gt;
-      &lt;li&gt;a multiplicação adicional pelo fator $(1+i)$ verifica-se apenas no cálculo do Valor Atual[cite: 78].&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F331" t="n">
-        <v>0</v>
-      </c>
-      <c r="G331" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="n">
-        <v>482</v>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Equivalência de Capitais</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>Rendas Perpétuas (Termos Ilimitados)</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;
@@ -19286,33 +19260,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F332" t="n">
-        <v>0</v>
-      </c>
-      <c r="G332" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="n">
+      <c r="F331" t="n">
+        <v>0</v>
+      </c>
+      <c r="G331" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
         <v>483</v>
       </c>
-      <c r="B333" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>Inglês</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr">
+      <c r="C332" t="inlineStr">
         <is>
           <t>Modal Verbs</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
+      <c r="D332" t="inlineStr">
         <is>
           <t>Modal Verbs (Verbos Modais)</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr">
+      <c r="E332" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Características Principais (Regras Gerais)&lt;/strong&gt;
@@ -19383,33 +19357,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F333" t="n">
-        <v>0</v>
-      </c>
-      <c r="G333" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="n">
+      <c r="F332" t="n">
+        <v>0</v>
+      </c>
+      <c r="G332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
         <v>484</v>
       </c>
-      <c r="B334" t="inlineStr">
+      <c r="B333" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr">
+      <c r="C333" t="inlineStr">
         <is>
           <t>Morfologia</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
+      <c r="D333" t="inlineStr">
         <is>
           <t>Concordância Verbal: Verbo "Haver" e Casos Especiais</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr">
+      <c r="E333" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Verbo "Haver" (Sentido de Existir/Ocorrer/Tempo Decorrido)&lt;/strong&gt;
@@ -19444,33 +19418,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F334" t="n">
-        <v>0</v>
-      </c>
-      <c r="G334" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="n">
+      <c r="F333" t="n">
+        <v>0</v>
+      </c>
+      <c r="G333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
         <v>485</v>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B334" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr">
+      <c r="C334" t="inlineStr">
         <is>
           <t>Morfologia</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
+      <c r="D334" t="inlineStr">
         <is>
           <t>Colocação Pronominal (Atrações e Regras)</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
+      <c r="E334" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Regra Geral do Português&lt;/strong&gt;
@@ -19501,33 +19475,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F335" t="n">
-        <v>0</v>
-      </c>
-      <c r="G335" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="n">
+      <c r="F334" t="n">
+        <v>0</v>
+      </c>
+      <c r="G334" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
         <v>486</v>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
+      <c r="C335" t="inlineStr">
         <is>
           <t>Pontuação</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
+      <c r="D335" t="inlineStr">
         <is>
           <t>Conectivos Deslocados, Dois-Pontos e Reticências</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr">
+      <c r="E335" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Vírgula e Conectivos Deslocados&lt;/strong&gt;
@@ -19552,6 +19526,74 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F335" t="n">
+        <v>0</v>
+      </c>
+      <c r="G335" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Ortografia e Acentuação</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Regras do Hífen (Novo Acordo Ortográfico)</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Regras Gerais de Prefixos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Letras Diferentes SE ATRAEM:&lt;/strong&gt; Se o prefixo termina com vogal e a segunda palavra começa com consoante ou vogal diferente, &lt;b&gt;junta-se tudo sem hífen&lt;/b&gt;.
+        &lt;ul&gt;
+          &lt;li&gt;&lt;i&gt;Ex: autoescola, infraestrutura, semiautomático, semicírculo, antivacinas, autoconhecimento.&lt;/i&gt;&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Letras Iguais SE REPELEM (Hífen):&lt;/strong&gt; Se a última letra do prefixo é igual à primeira letra do termo seguinte, &lt;b&gt;usa-se o hífen obrigatoriamente&lt;/b&gt;.
+        &lt;ul&gt;
+          &lt;li&gt;&lt;i&gt;Ex: micro-ondas, anti-inflamatório, contra-ataque.&lt;/i&gt;&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Casos com "H", "R" e "S"&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Diante de H (Hífen Permanente):&lt;/strong&gt; Qualquer que seja o prefixo, se a próxima palavra inicia com "h", há hífen.
+        &lt;ul&gt;
+          &lt;li&gt;&lt;i&gt;Ex: anti-higiênico, super-homem, auto-hipnose.&lt;/i&gt;&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Consoantes "R" e "S" após Vogal:&lt;/strong&gt; Quando o prefixo termina em vogal e a palavra seguinte começa com "r" ou "s", &lt;b&gt;dobram-se as consoantes e elimina-se o hífen&lt;/b&gt;.
+        &lt;ul&gt;
+          &lt;li&gt;&lt;i&gt;Ex: antissocial, minissaia, autorretrato, ultrassom, antirrugas.&lt;/i&gt;&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Prefixos Especiais (Exceções Comuns)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;i&gt;Ex, Sem, Além, Aquém, Recém, Pós, Pré, Pró:&lt;/i&gt; &lt;b&gt;Sempre com hífen.&lt;/b&gt;&lt;/li&gt;
+      &lt;li&gt;&lt;i&gt;Sub:&lt;/i&gt; Hífen apenas diante de B, H ou R (ex: &lt;i&gt;sub-base, sub-reino, sub-humano&lt;/i&gt;). Nas demais juntas (ex: &lt;i&gt;subemprego&lt;/i&gt;).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F336" t="n">
         <v>0</v>
       </c>
@@ -19562,7 +19604,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -19577,44 +19619,25 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Regras do Hífen (Novo Acordo Ortográfico)</t>
+          <t>Emprego de S com som de Z</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Regras Gerais de Prefixos&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Letras Diferentes SE ATRAEM:&lt;/strong&gt; Se o prefixo termina com vogal e a segunda palavra começa com consoante ou vogal diferente, &lt;b&gt;junta-se tudo sem hífen&lt;/b&gt;.
-        &lt;ul&gt;
-          &lt;li&gt;&lt;i&gt;Ex: autoescola, infraestrutura, semiautomático, semicírculo, antivacinas, autoconhecimento.&lt;/i&gt;&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Letras Iguais SE REPELEM (Hífen):&lt;/strong&gt; Se a última letra do prefixo é igual à primeira letra do termo seguinte, &lt;b&gt;usa-se o hífen obrigatoriamente&lt;/b&gt;.
-        &lt;ul&gt;
-          &lt;li&gt;&lt;i&gt;Ex: micro-ondas, anti-inflamatório, contra-ataque.&lt;/i&gt;&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Casos com "H", "R" e "S"&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Diante de H (Hífen Permanente):&lt;/strong&gt; Qualquer que seja o prefixo, se a próxima palavra inicia com "h", há hífen.
-        &lt;ul&gt;
-          &lt;li&gt;&lt;i&gt;Ex: anti-higiênico, super-homem, auto-hipnose.&lt;/i&gt;&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Consoantes "R" e "S" após Vogal:&lt;/strong&gt; Quando o prefixo termina em vogal e a palavra seguinte começa com "r" ou "s", &lt;b&gt;dobram-se as consoantes e elimina-se o hífen&lt;/b&gt;.
-        &lt;ul&gt;
-          &lt;li&gt;&lt;i&gt;Ex: antissocial, minissaia, autorretrato, ultrassom, antirrugas.&lt;/i&gt;&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Prefixos Especiais (Exceções Comuns)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;i&gt;Ex, Sem, Além, Aquém, Recém, Pós, Pré, Pró:&lt;/i&gt; &lt;b&gt;Sempre com hífen.&lt;/b&gt;&lt;/li&gt;
-      &lt;li&gt;&lt;i&gt;Sub:&lt;/i&gt; Hífen apenas diante de B, H ou R (ex: &lt;i&gt;sub-base, sub-reino, sub-humano&lt;/i&gt;). Nas demais juntas (ex: &lt;i&gt;subemprego&lt;/i&gt;).&lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Sufixos de Adjetivos Pátrios, Títulos ou Estado:&lt;/strong&gt; -ês, -esa, -isa.
+    &lt;ul&gt;
+      &lt;li&gt;&lt;i&gt;Ex: português, burguesia, profetisa, baronesa.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;burguezia&lt;/s&gt;, &lt;s&gt;baroneza&lt;/s&gt;).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Derivados de Radicais com "S":&lt;/strong&gt; Mantém-se a grafia original do verbo ou substantivo base.
+    &lt;ul&gt;
+      &lt;li&gt;&lt;i&gt;Ex: pesquisa $\rightarrow$ pesquisar; improviso $\rightarrow$ improvisar; aviso $\rightarrow$ avisar.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;pesquiza&lt;/s&gt;, &lt;s&gt;improvizo&lt;/s&gt;).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Após Ditongos:&lt;/strong&gt; Usa-se o "s" quando houver encontro vocálico precedente.
+    &lt;ul&gt;
+      &lt;li&gt;&lt;i&gt;Ex: coisa, causa, lousa, querosene.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;querozene&lt;/s&gt;).&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -19628,74 +19651,25 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
+      <c r="A338" t="n">
+        <v>489</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Português</t>
+          <t>Contratação</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Ortografia e Acentuação</t>
+          <t>Lei Complementar Nº 123 - 2006 e Lei Complementar Nº 155 - 2016</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Emprego de S com som de Z</t>
+          <t>Estatuto Nacional da Microempresa e da Empresa de Pequeno Porte (LC 123) - Aquisições Públicas e Acesso a Mercados</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Sufixos de Adjetivos Pátrios, Títulos ou Estado:&lt;/strong&gt; -ês, -esa, -isa.
-    &lt;ul&gt;
-      &lt;li&gt;&lt;i&gt;Ex: português, burguesia, profetisa, baronesa.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;burguezia&lt;/s&gt;, &lt;s&gt;baroneza&lt;/s&gt;).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Derivados de Radicais com "S":&lt;/strong&gt; Mantém-se a grafia original do verbo ou substantivo base.
-    &lt;ul&gt;
-      &lt;li&gt;&lt;i&gt;Ex: pesquisa $\rightarrow$ pesquisar; improviso $\rightarrow$ improvisar; aviso $\rightarrow$ avisar.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;pesquiza&lt;/s&gt;, &lt;s&gt;improvizo&lt;/s&gt;).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Após Ditongos:&lt;/strong&gt; Usa-se o "s" quando houver encontro vocálico precedente.
-    &lt;ul&gt;
-      &lt;li&gt;&lt;i&gt;Ex: coisa, causa, lousa, querosene.&lt;/i&gt; (Gatilho de erro da banca: &lt;s&gt;querozene&lt;/s&gt;).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F338" t="n">
-        <v>0</v>
-      </c>
-      <c r="G338" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="n">
-        <v>489</v>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Contratação</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Lei Complementar Nº 123 - 2006 e Lei Complementar Nº 155 - 2016</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>Estatuto Nacional da Microempresa e da Empresa de Pequeno Porte (LC 123) - Aquisições Públicas e Acesso a Mercados</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Comprovação de Regularidade Fiscal e Trabalhista&lt;/b&gt;
@@ -19797,33 +19771,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F339" t="n">
-        <v>0</v>
-      </c>
-      <c r="G339" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="n">
+      <c r="F338" t="n">
+        <v>0</v>
+      </c>
+      <c r="G338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
         <v>490</v>
       </c>
-      <c r="B340" t="inlineStr">
+      <c r="B339" t="inlineStr">
         <is>
           <t>Contratação</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr">
+      <c r="C339" t="inlineStr">
         <is>
           <t>Lei Complementar Nº 123 - 2006 e Lei Complementar Nº 155 - 2016</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr">
+      <c r="D339" t="inlineStr">
         <is>
           <t>Alterações na Apuração, Limites e Regras Gerais do Simples Nacional (LC 155)</t>
         </is>
       </c>
-      <c r="E340" t="inlineStr">
+      <c r="E339" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Limites de Receita Bruta (Ano-Calendário)&lt;/b&gt;
@@ -19886,33 +19860,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F340" t="n">
-        <v>0</v>
-      </c>
-      <c r="G340" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="n">
+      <c r="F339" t="n">
+        <v>0</v>
+      </c>
+      <c r="G339" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
         <v>491</v>
       </c>
-      <c r="B341" t="inlineStr">
+      <c r="B340" t="inlineStr">
         <is>
           <t>Contratação</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr">
+      <c r="C340" t="inlineStr">
         <is>
           <t>Lei Complementar Nº 123 - 2006 e Lei Complementar Nº 155 - 2016</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr">
+      <c r="D340" t="inlineStr">
         <is>
           <t>Investidor-Anjo e Programa de Fomento Urbano (LC 155)</t>
         </is>
       </c>
-      <c r="E341" t="inlineStr">
+      <c r="E340" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Figura do Investidor-Anjo&lt;/b&gt;
@@ -19964,33 +19938,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F341" t="n">
-        <v>0</v>
-      </c>
-      <c r="G341" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="n">
+      <c r="F340" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
         <v>492</v>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B341" t="inlineStr">
         <is>
           <t>Estatística</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
+      <c r="C341" t="inlineStr">
         <is>
           <t>Regressão Linear Simples</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr">
+      <c r="D341" t="inlineStr">
         <is>
           <t>Correlação Linear</t>
         </is>
       </c>
-      <c r="E342" t="inlineStr">
+      <c r="E341" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Conceito Geral&lt;/b&gt;
@@ -20034,33 +20008,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F342" t="n">
-        <v>0</v>
-      </c>
-      <c r="G342" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="n">
+      <c r="F341" t="n">
+        <v>0</v>
+      </c>
+      <c r="G341" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
         <v>493</v>
       </c>
-      <c r="B343" t="inlineStr">
+      <c r="B342" t="inlineStr">
         <is>
           <t>Estatística</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr">
+      <c r="C342" t="inlineStr">
         <is>
           <t>Regressão Linear Simples</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr">
+      <c r="D342" t="inlineStr">
         <is>
           <t>Regressão Linear Simples</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr">
+      <c r="E342" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Conceito e Modelo Populacional&lt;/b&gt;
@@ -20103,33 +20077,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F343" t="n">
-        <v>0</v>
-      </c>
-      <c r="G343" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="n">
+      <c r="F342" t="n">
+        <v>0</v>
+      </c>
+      <c r="G342" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
         <v>494</v>
       </c>
-      <c r="B344" t="inlineStr">
+      <c r="B343" t="inlineStr">
         <is>
           <t>Estatística</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
+      <c r="C343" t="inlineStr">
         <is>
           <t>Regressão Linear Simples</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr">
+      <c r="D343" t="inlineStr">
         <is>
           <t>Análise de Variância da Regressão (ANOVA)</t>
         </is>
       </c>
-      <c r="E344" t="inlineStr">
+      <c r="E343" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Objetivo do Teste&lt;/b&gt;
@@ -20189,33 +20163,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F344" t="n">
-        <v>0</v>
-      </c>
-      <c r="G344" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="n">
+      <c r="F343" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
         <v>495</v>
       </c>
-      <c r="B345" t="inlineStr">
+      <c r="B344" t="inlineStr">
         <is>
           <t>Estatística</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
+      <c r="C344" t="inlineStr">
         <is>
           <t>Números Índices</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr">
+      <c r="D344" t="inlineStr">
         <is>
           <t>Números Índices e Números Relativos</t>
         </is>
       </c>
-      <c r="E345" t="inlineStr">
+      <c r="E344" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Números Índices&lt;/b&gt;
@@ -20259,33 +20233,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F345" t="n">
-        <v>0</v>
-      </c>
-      <c r="G345" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="n">
+      <c r="F344" t="n">
+        <v>0</v>
+      </c>
+      <c r="G344" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
         <v>496</v>
       </c>
-      <c r="B346" t="inlineStr">
+      <c r="B345" t="inlineStr">
         <is>
           <t>Estatística</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr">
+      <c r="C345" t="inlineStr">
         <is>
           <t>Números Índices</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr">
+      <c r="D345" t="inlineStr">
         <is>
           <t>Índices Agregativos Simples</t>
         </is>
       </c>
-      <c r="E346" t="inlineStr">
+      <c r="E345" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Conceito&lt;/b&gt;
@@ -20321,33 +20295,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F346" t="n">
-        <v>0</v>
-      </c>
-      <c r="G346" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="n">
+      <c r="F345" t="n">
+        <v>0</v>
+      </c>
+      <c r="G345" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
         <v>497</v>
       </c>
-      <c r="B347" t="inlineStr">
+      <c r="B346" t="inlineStr">
         <is>
           <t>Estatística</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr">
+      <c r="C346" t="inlineStr">
         <is>
           <t>Números Índices</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr">
+      <c r="D346" t="inlineStr">
         <is>
           <t>Índices Agregativos Ponderados</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr">
+      <c r="E346" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Conceito&lt;/b&gt;
@@ -20384,6 +20358,56 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F346" t="n">
+        <v>0</v>
+      </c>
+      <c r="G346" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>498</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Estatística</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Números Índices</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Mudança de Base em Números Índices</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Base Fixa para Base Fixa&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;processo direto de realocação do período de referência&lt;/li&gt;
+            &lt;li&gt;divide-se a série inicial pelo valor do índice que se encontra no novo período-base desejado (multiplicando-se o resultado por 100)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Base Fixa para Base Móvel&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;transforma a série para que cada período referencie apenas seu antecessor imediato&lt;/li&gt;
+            &lt;li&gt;divide-se o índice do período atual pelo índice do período imediatamente anterior ($I_{t-1, t} = \frac{I_{0,t}}{I_{0,t-1}}$)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Base Móvel para Base Fixa&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;reconstrói a série contínua a partir de variações encadeadas&lt;/li&gt;
+            &lt;li&gt;realiza-se a multiplicação sucessiva dos índices (desde que a propriedade circular seja satisfeita no conjunto)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F347" t="n">
         <v>0</v>
       </c>
@@ -20393,74 +20417,24 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Estatística</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Números Índices</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Mudança de Base em Números Índices</t>
+          <t>NR 17 (Ergonomia) - Elementos da Organização do Trabalho</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-    &lt;li&gt;&lt;b&gt;Base Fixa para Base Fixa&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;processo direto de realocação do período de referência&lt;/li&gt;
-            &lt;li&gt;divide-se a série inicial pelo valor do índice que se encontra no novo período-base desejado (multiplicando-se o resultado por 100)&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-    &lt;li&gt;&lt;b&gt;Base Fixa para Base Móvel&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;transforma a série para que cada período referencie apenas seu antecessor imediato&lt;/li&gt;
-            &lt;li&gt;divide-se o índice do período atual pelo índice do período imediatamente anterior ($I_{t-1, t} = \frac{I_{0,t}}{I_{0,t-1}}$)&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-    &lt;li&gt;&lt;b&gt;Base Móvel para Base Fixa&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;reconstrói a série contínua a partir de variações encadeadas&lt;/li&gt;
-            &lt;li&gt;realiza-se a multiplicação sucessiva dos índices (desde que a propriedade circular seja satisfeita no conjunto)&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F348" t="n">
-        <v>0</v>
-      </c>
-      <c r="G348" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="n">
-        <v>499</v>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>NR 17 (Ergonomia) - Elementos da Organização do Trabalho</t>
-        </is>
-      </c>
-      <c r="E349" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;A ergonomia não se limita ao mobiliário. A NR 17 estabelece que a &lt;b&gt;organização do trabalho&lt;/b&gt; deve ter em consideração, no mínimo, os seguintes aspetos:
@@ -20476,6 +20450,65 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F348" t="n">
+        <v>0</v>
+      </c>
+      <c r="G348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>500</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Investigação de Acidentes de Trabalho: Hierarquia e Tipologia das Causas</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Causas Imediatas (Falhas Ativas):&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;São as razões mais &lt;b&gt;óbvias&lt;/b&gt; e evidenciadas na &lt;b&gt;proximidade temporal e espacial&lt;/b&gt; das consequências.&lt;/li&gt;
+            &lt;li&gt;Exemplos: um erro humano agudo (ato inseguro) ou a quebra de uma peça no momento do acidente (condição insegura).&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Fatores Subjacentes (Causas Básicas/Sistêmicas):&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;São razões &lt;b&gt;sistêmicas ou organizacionais menos evidentes&lt;/b&gt;, porém necessárias para que ocorra o evento adverso.&lt;/li&gt;
+            &lt;li&gt;Representam as falhas de gestão, cultura de segurança tolerante ao risco, falta de treinamento ou procedimentos inadequados que abrem caminho para a causa imediata.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Causa-Raiz (Root Cause):&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;São as &lt;b&gt;condições iniciadoras primárias&lt;/b&gt; que possibilitam o surgimento de todos os outros fatores relacionados ao evento adverso.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Fatores Latentes:&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;São situações frequentemente &lt;b&gt;remotas no tempo&lt;/b&gt; (ex: um erro de projeto ou de planejamento ocorrido anos antes, que fica adormecido no sistema até interagir com uma falha local).&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Princípio da Multicausalidade:&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Situações em que podem ser identificados &lt;b&gt;diversos fatores conjugados&lt;/b&gt; para um evento adverso (um acidente nunca tem apenas uma causa isolada).&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F349" t="n">
         <v>0</v>
       </c>
@@ -20485,7 +20518,7 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -20494,74 +20527,15 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Engenharia do Trabalho</t>
+          <t>Planejamento e Controle da Produção</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Investigação de Acidentes de Trabalho: Hierarquia e Tipologia das Causas</t>
+          <t>Hierarquia do PCP: S&amp;OP, Plano Agregado (PAP), Plano Mestre (PMP) e MRP</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-    &lt;li&gt;&lt;b&gt;Causas Imediatas (Falhas Ativas):&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;São as razões mais &lt;b&gt;óbvias&lt;/b&gt; e evidenciadas na &lt;b&gt;proximidade temporal e espacial&lt;/b&gt; das consequências.&lt;/li&gt;
-            &lt;li&gt;Exemplos: um erro humano agudo (ato inseguro) ou a quebra de uma peça no momento do acidente (condição insegura).&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-    &lt;li&gt;&lt;b&gt;Fatores Subjacentes (Causas Básicas/Sistêmicas):&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;São razões &lt;b&gt;sistêmicas ou organizacionais menos evidentes&lt;/b&gt;, porém necessárias para que ocorra o evento adverso.&lt;/li&gt;
-            &lt;li&gt;Representam as falhas de gestão, cultura de segurança tolerante ao risco, falta de treinamento ou procedimentos inadequados que abrem caminho para a causa imediata.&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-    &lt;li&gt;&lt;b&gt;Causa-Raiz (Root Cause):&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;São as &lt;b&gt;condições iniciadoras primárias&lt;/b&gt; que possibilitam o surgimento de todos os outros fatores relacionados ao evento adverso.&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-    &lt;li&gt;&lt;b&gt;Fatores Latentes:&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;São situações frequentemente &lt;b&gt;remotas no tempo&lt;/b&gt; (ex: um erro de projeto ou de planejamento ocorrido anos antes, que fica adormecido no sistema até interagir com uma falha local).&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-    &lt;li&gt;&lt;b&gt;Princípio da Multicausalidade:&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;Situações em que podem ser identificados &lt;b&gt;diversos fatores conjugados&lt;/b&gt; para um evento adverso (um acidente nunca tem apenas uma causa isolada).&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F350" t="n">
-        <v>0</v>
-      </c>
-      <c r="G350" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="n">
-        <v>501</v>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>Planejamento e Controle da Produção</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>Hierarquia do PCP: S&amp;OP, Plano Agregado (PAP), Plano Mestre (PMP) e MRP</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;S&amp;OP (Sales and Operations Planning - Planejamento de Vendas e Operações):&lt;/b&gt;
@@ -20599,6 +20573,51 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F350" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>502</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Gestão da Informação</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Gestão de Recursos Informacionais (GRI)</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+            &lt;li&gt;Disciplina administrativa que reconhece a &lt;b&gt;informação como um ativo corporativo crítico e estratégico&lt;/b&gt; (tão vital quanto dinheiro, máquinas ou pessoas), gerida através dos pilares de Pessoas, Processos e Tecnologia.&lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Perspetiva Tecnológica (Foco Operacional e Infraestrutura):&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Foca na "ferramenta": os sistemas, as bases de dados, o hardware e o software.&lt;/li&gt;
+            &lt;li&gt;&lt;i&gt;Atividades cobradas em prova:&lt;/i&gt; planeamento de dados e da capacidade das aplicações, integração de sistemas, administração de dados e desenvolvimento de sistemas de informação.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Perspetiva Integrativa (Foco Estratégico e Gerencial):&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Foca no "valor" e na mudança de cultura: a informação deixa de ser um mero subproduto da TI para guiar ativamente as decisões do negócio.&lt;/li&gt;
+            &lt;li&gt;&lt;i&gt;Atividades cobradas em prova:&lt;/i&gt; &lt;b&gt;reconhecimento da informação como um recurso&lt;/b&gt;, alinhamento da tecnologia aos objetivos organizacionais e promoção de mudança cultural e de gestão.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F351" t="n">
         <v>0</v>
       </c>
@@ -20608,7 +20627,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -20617,60 +20636,15 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Gestão da Informação</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Gestão de Recursos Informacionais (GRI)</t>
+          <t>NR 17 (Ergonomia): principais áreas de avaliação</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-            &lt;li&gt;Disciplina administrativa que reconhece a &lt;b&gt;informação como um ativo corporativo crítico e estratégico&lt;/b&gt; (tão vital quanto dinheiro, máquinas ou pessoas), gerida através dos pilares de Pessoas, Processos e Tecnologia.&lt;/li&gt;
-    &lt;li&gt;&lt;b&gt;Perspetiva Tecnológica (Foco Operacional e Infraestrutura):&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;Foca na "ferramenta": os sistemas, as bases de dados, o hardware e o software.&lt;/li&gt;
-            &lt;li&gt;&lt;i&gt;Atividades cobradas em prova:&lt;/i&gt; planeamento de dados e da capacidade das aplicações, integração de sistemas, administração de dados e desenvolvimento de sistemas de informação.&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-    &lt;li&gt;&lt;b&gt;Perspetiva Integrativa (Foco Estratégico e Gerencial):&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;Foca no "valor" e na mudança de cultura: a informação deixa de ser um mero subproduto da TI para guiar ativamente as decisões do negócio.&lt;/li&gt;
-            &lt;li&gt;&lt;i&gt;Atividades cobradas em prova:&lt;/i&gt; &lt;b&gt;reconhecimento da informação como um recurso&lt;/b&gt;, alinhamento da tecnologia aos objetivos organizacionais e promoção de mudança cultural e de gestão.&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F352" t="n">
-        <v>0</v>
-      </c>
-      <c r="G352" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="n">
-        <v>503</v>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>NR 17 (Ergonomia): principais áreas de avaliação</t>
-        </is>
-      </c>
-      <c r="E353" t="inlineStr">
         <is>
           <t>&lt;ul&gt; 
             &lt;li&gt;Avaliação das situações de trabalho.&lt;/li&gt;
@@ -20682,33 +20656,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F353" t="n">
-        <v>0</v>
-      </c>
-      <c r="G353" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="n">
+      <c r="F352" t="n">
+        <v>0</v>
+      </c>
+      <c r="G352" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
         <v>504</v>
       </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr">
+      <c r="D353" t="inlineStr">
         <is>
           <t>NR 17 (Ergonomia): A Organização do Trabalho</t>
         </is>
       </c>
-      <c r="E354" t="inlineStr">
+      <c r="E353" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;A organização do trabalho deve levar em consideração:
@@ -20724,33 +20698,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F354" t="n">
-        <v>0</v>
-      </c>
-      <c r="G354" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="n">
+      <c r="F353" t="n">
+        <v>0</v>
+      </c>
+      <c r="G353" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
         <v>505</v>
       </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr">
+      <c r="D354" t="inlineStr">
         <is>
           <t>NR 17 (Ergonomia): O Campo de Aplicação</t>
         </is>
       </c>
-      <c r="E355" t="inlineStr">
+      <c r="E354" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;Aplica-se a &lt;b&gt;todas as situações de trabalho&lt;/b&gt; das organizações e dos órgãos públicos da administração direta e indireta.&lt;/li&gt;
@@ -20759,33 +20733,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F355" t="n">
-        <v>0</v>
-      </c>
-      <c r="G355" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="n">
+      <c r="F354" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
         <v>506</v>
       </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
+      <c r="D355" t="inlineStr">
         <is>
           <t>NR 17 (Ergonomia): Avaliação das situações de trabalho</t>
         </is>
       </c>
-      <c r="E356" t="inlineStr">
+      <c r="E355" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Avaliação Ergonómica Preliminar (AEP):&lt;/b&gt; Abordagem inicial qualitativa, semiquantitativa ou quantitativa para identificar perigos e planear medidas.&lt;/li&gt;
@@ -20794,33 +20768,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F356" t="n">
-        <v>0</v>
-      </c>
-      <c r="G356" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="n">
+      <c r="F355" t="n">
+        <v>0</v>
+      </c>
+      <c r="G355" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
         <v>507</v>
       </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
+      <c r="D356" t="inlineStr">
         <is>
           <t>NR 17 (Ergonomia): Condições de Conforto</t>
         </is>
       </c>
-      <c r="E357" t="inlineStr">
+      <c r="E356" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Iluminação:&lt;/b&gt; Deve evitar ofuscamento e reflexos. Os níveis mínimos são estabelecidos pela NHO 11 da Fundacentro.&lt;/li&gt;
@@ -20829,33 +20803,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F357" t="n">
-        <v>0</v>
-      </c>
-      <c r="G357" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="n">
+      <c r="F356" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
         <v>320</v>
       </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr">
+      <c r="D357" t="inlineStr">
         <is>
           <t>NR 17</t>
         </is>
       </c>
-      <c r="E358" t="inlineStr">
+      <c r="E357" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Manuseio de cargas&lt;/strong&gt;
@@ -20889,33 +20863,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F358" t="n">
-        <v>0</v>
-      </c>
-      <c r="G358" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="n">
+      <c r="F357" t="n">
+        <v>0</v>
+      </c>
+      <c r="G357" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
         <v>508</v>
       </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
+      <c r="D358" t="inlineStr">
         <is>
           <t>Distribuição Física (Outbound Logistics)</t>
         </is>
       </c>
-      <c r="E359" t="inlineStr">
+      <c r="E358" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Conceito Central&lt;/b&gt;
@@ -20940,33 +20914,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F359" t="n">
-        <v>0</v>
-      </c>
-      <c r="G359" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="n">
+      <c r="F358" t="n">
+        <v>0</v>
+      </c>
+      <c r="G358" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
         <v>509</v>
       </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr">
+      <c r="D359" t="inlineStr">
         <is>
           <t>Logística de Suprimentos (Inbound Logistics / Administração de Materiais)</t>
         </is>
       </c>
-      <c r="E360" t="inlineStr">
+      <c r="E359" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Conceito Central&lt;/b&gt;
@@ -20992,33 +20966,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F360" t="n">
-        <v>0</v>
-      </c>
-      <c r="G360" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="n">
+      <c r="F359" t="n">
+        <v>0</v>
+      </c>
+      <c r="G359" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
         <v>510</v>
       </c>
-      <c r="B361" t="inlineStr">
+      <c r="B360" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
+      <c r="C360" t="inlineStr">
         <is>
           <t>Ortografia e Acentuação</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
+      <c r="D360" t="inlineStr">
         <is>
           <t>X vs CH</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr">
+      <c r="E360" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Obrigatoriedade do "X"&lt;/strong&gt;
@@ -21042,33 +21016,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F361" t="n">
-        <v>0</v>
-      </c>
-      <c r="G361" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="n">
+      <c r="F360" t="n">
+        <v>0</v>
+      </c>
+      <c r="G360" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
         <v>511</v>
       </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr">
+      <c r="D361" t="inlineStr">
         <is>
           <t>Gestão Económica e Modelo GECON</t>
         </is>
       </c>
-      <c r="E362" t="inlineStr">
+      <c r="E361" t="inlineStr">
         <is>
           <t>&lt;div&gt;
     &lt;ul&gt;
@@ -21100,33 +21074,33 @@
 &lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F362" t="n">
-        <v>0</v>
-      </c>
-      <c r="G362" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="n">
+      <c r="F361" t="n">
+        <v>0</v>
+      </c>
+      <c r="G361" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
         <v>512</v>
       </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
+      <c r="D362" t="inlineStr">
         <is>
           <t>Princípios da Engenharia Económica e EVA</t>
         </is>
       </c>
-      <c r="E363" t="inlineStr">
+      <c r="E362" t="inlineStr">
         <is>
           <t>&lt;div&gt;
     &lt;ul&gt;
@@ -21159,33 +21133,33 @@
 &lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F363" t="n">
-        <v>0</v>
-      </c>
-      <c r="G363" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="n">
+      <c r="F362" t="n">
+        <v>0</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
         <v>513</v>
       </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr">
+      <c r="D363" t="inlineStr">
         <is>
           <t>Terminologia de Custos e Ciclo de Vida</t>
         </is>
       </c>
-      <c r="E364" t="inlineStr">
+      <c r="E363" t="inlineStr">
         <is>
           <t>&lt;div&gt;
     &lt;ul&gt;
@@ -21228,33 +21202,33 @@
 &lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F364" t="n">
-        <v>0</v>
-      </c>
-      <c r="G364" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="n">
+      <c r="F363" t="n">
+        <v>0</v>
+      </c>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
         <v>514</v>
       </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr">
+      <c r="D364" t="inlineStr">
         <is>
           <t>Microeconomia e Ponto de Equilíbrio</t>
         </is>
       </c>
-      <c r="E365" t="inlineStr">
+      <c r="E364" t="inlineStr">
         <is>
           <t>&lt;div&gt;
     &lt;ul&gt;
@@ -21282,33 +21256,33 @@
 &lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F365" t="n">
-        <v>0</v>
-      </c>
-      <c r="G365" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="n">
+      <c r="F364" t="n">
+        <v>0</v>
+      </c>
+      <c r="G364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
         <v>515</v>
       </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
+      <c r="D365" t="inlineStr">
         <is>
           <t>Estudo de Mercado e Procura</t>
         </is>
       </c>
-      <c r="E366" t="inlineStr">
+      <c r="E365" t="inlineStr">
         <is>
           <t>&lt;div&gt;
     &lt;ul&gt;
@@ -21338,33 +21312,33 @@
 &lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F366" t="n">
-        <v>0</v>
-      </c>
-      <c r="G366" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="n">
+      <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
         <v>516</v>
       </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr">
+      <c r="D366" t="inlineStr">
         <is>
           <t>Engenharia de Projeto e Tecnologias</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr">
+      <c r="E366" t="inlineStr">
         <is>
           <t>&lt;div&gt;
     &lt;ul&gt;
@@ -21397,33 +21371,33 @@
 &lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F367" t="n">
-        <v>0</v>
-      </c>
-      <c r="G367" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="n">
+      <c r="F366" t="n">
+        <v>0</v>
+      </c>
+      <c r="G366" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
         <v>517</v>
       </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr">
+      <c r="D367" t="inlineStr">
         <is>
           <t>Investimentos e Financiamento</t>
         </is>
       </c>
-      <c r="E368" t="inlineStr">
+      <c r="E367" t="inlineStr">
         <is>
           <t>&lt;div&gt;
     &lt;ul&gt;
@@ -21456,33 +21430,33 @@
 &lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F368" t="n">
-        <v>0</v>
-      </c>
-      <c r="G368" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="n">
+      <c r="F367" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
         <v>518</v>
       </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
+      <c r="D368" t="inlineStr">
         <is>
           <t>Avaliação Financeira (VPL, TIR e VAUE)</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr">
+      <c r="E368" t="inlineStr">
         <is>
           <t>&lt;div&gt;
     &lt;ul&gt;
@@ -21515,35 +21489,35 @@
 &lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F369" t="n">
-        <v>0</v>
-      </c>
-      <c r="G369" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
+      <c r="F368" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
         <is>
           <t>519</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
         <is>
           <t>Gestão Econômica</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
+      <c r="D369" t="inlineStr">
         <is>
           <t>Indicadores Agropecuários e Agroindustriais</t>
         </is>
       </c>
-      <c r="E370" t="inlineStr">
+      <c r="E369" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
         &lt;li&gt;&lt;b&gt;Medidas de ciclo produtivo&lt;/b&gt;
@@ -21556,33 +21530,35 @@
     &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F370" t="n">
-        <v>0</v>
-      </c>
-      <c r="G370" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="n">
-        <v>520</v>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
+      <c r="F369" t="n">
+        <v>0</v>
+      </c>
+      <c r="G369" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
         <is>
           <t>Indústria 4.0</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
+      <c r="D370" t="inlineStr">
         <is>
           <t>Internet das Coisas (IoT - Internet of Things)</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr">
+      <c r="E370" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
@@ -21598,36 +21574,42 @@
             &lt;li&gt;base para a manutenção preditiva&lt;/li&gt;
         &lt;/ul&gt;
     &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F371" t="n">
-        <v>0</v>
-      </c>
-      <c r="G371" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="n">
+&lt;li&gt;&lt;b&gt;Aplicação na logística&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;rastreamento de frotas, contêineres e cargas em tempo real via sensores&lt;/li&gt;
+            &lt;li&gt;monitoramento de telemetria, temperatura e umidade para cargas perecíveis&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>0</v>
+      </c>
+      <c r="G370" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
         <v>521</v>
       </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
         <is>
           <t>Indústria 4.0</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
+      <c r="D371" t="inlineStr">
         <is>
           <t>Sistemas Ciberfísicos (CPS - Cyber-Physical Systems)</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr">
+      <c r="E371" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
@@ -21646,33 +21628,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F372" t="n">
-        <v>0</v>
-      </c>
-      <c r="G372" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="n">
+      <c r="F371" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
         <v>522</v>
       </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
         <is>
           <t>Indústria 4.0</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
+      <c r="D372" t="inlineStr">
         <is>
           <t>Computação em Nuvem (Cloud Computing)</t>
         </is>
       </c>
-      <c r="E373" t="inlineStr">
+      <c r="E372" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
@@ -21691,33 +21673,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F373" t="n">
-        <v>0</v>
-      </c>
-      <c r="G373" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="n">
-        <v>523</v>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
+      <c r="F372" t="n">
+        <v>0</v>
+      </c>
+      <c r="G372" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
         <is>
           <t>Indústria 4.0</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr">
+      <c r="D373" t="inlineStr">
         <is>
           <t>Big Data e Analytics (Megadados e Análise de Dados)</t>
         </is>
       </c>
-      <c r="E374" t="inlineStr">
+      <c r="E373" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
@@ -21733,6 +21717,64 @@
             &lt;li&gt;previsão de demanda com maior precisão e ajuste de capacidade produtiva&lt;/li&gt;
         &lt;/ul&gt;
     &lt;/li&gt;
+&lt;li&gt;&lt;b&gt;Aplicação na logística&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;apoio à tomada de decisões estratégicas, previsibilidade de riscos e otimização de malhas logísticas complexas&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>0</v>
+      </c>
+      <c r="G373" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Simulação e Gêmeos Digitais (Digital Twins)</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;réplica virtual exata de um produto, processo ou sistema físico (como armazéns e frotas)&lt;/li&gt;
+            &lt;li&gt;alimentada com dados em tempo real via IoT&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;testes e otimizações de &lt;i&gt;layouts&lt;/i&gt; e processos de manufatura sem interrupção da linha física&lt;/li&gt;
+            &lt;li&gt;redução do tempo e custo de comissionamento de novos equipamentos na fábrica&lt;/li&gt;
+            &lt;li&gt;simulação de cenários de falha para treinamento e mitigação de riscos industriais&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na logística 4.0&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;simulação de cenários e identificação de gargalos operacionais na cadeia de suprimentos&lt;/li&gt;
+            &lt;li&gt;teste de fluxos de materiais, redes de transporte e roteirização antes da implementação física&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -21745,7 +21787,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -21759,55 +21801,10 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Simulação e Gêmeos Digitais (Digital Twins)</t>
+          <t>Manufatura Aditiva (Impressão 3D)</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;réplica virtual exata de um produto, processo ou sistema físico&lt;/li&gt;
-            &lt;li&gt;alimentada com dados em tempo real via IoT&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;testes e otimizações de &lt;i&gt;layout&lt;/i&gt; e processos sem interrupção da linha física&lt;/li&gt;
-            &lt;li&gt;redução do tempo e custo de comissionamento de novos equipamentos&lt;/li&gt;
-            &lt;li&gt;simulação de cenários de falha para treinamento e mitigação de riscos&lt;/li&gt;
-        &lt;/ul&gt;
-    &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F375" t="n">
-        <v>0</v>
-      </c>
-      <c r="G375" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="n">
-        <v>525</v>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>Indústria 4.0</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>Manufatura Aditiva (Impressão 3D)</t>
-        </is>
-      </c>
-      <c r="E376" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
@@ -21826,33 +21823,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F376" t="n">
-        <v>0</v>
-      </c>
-      <c r="G376" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="n">
+      <c r="F375" t="n">
+        <v>0</v>
+      </c>
+      <c r="G375" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
         <v>526</v>
       </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C377" t="inlineStr">
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
         <is>
           <t>Indústria 4.0</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
+      <c r="D376" t="inlineStr">
         <is>
           <t>Robótica Autônoma</t>
         </is>
       </c>
-      <c r="E377" t="inlineStr">
+      <c r="E376" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
@@ -21871,33 +21868,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F377" t="n">
-        <v>0</v>
-      </c>
-      <c r="G377" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="n">
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
         <v>527</v>
       </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
         <is>
           <t>Indústria 4.0</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr">
+      <c r="D377" t="inlineStr">
         <is>
           <t>Segurança Cibernética (Cybersecurity)</t>
         </is>
       </c>
-      <c r="E378" t="inlineStr">
+      <c r="E377" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
@@ -21916,33 +21913,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F378" t="n">
-        <v>0</v>
-      </c>
-      <c r="G378" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="n">
+      <c r="F377" t="n">
+        <v>0</v>
+      </c>
+      <c r="G377" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
         <v>528</v>
       </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C379" t="inlineStr">
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
         <is>
           <t>Indústria 4.0</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr">
+      <c r="D378" t="inlineStr">
         <is>
           <t>Integração de Sistemas (Horizontal e Vertical)</t>
         </is>
       </c>
-      <c r="E379" t="inlineStr">
+      <c r="E378" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
@@ -21961,33 +21958,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F379" t="n">
-        <v>0</v>
-      </c>
-      <c r="G379" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="n">
+      <c r="F378" t="n">
+        <v>0</v>
+      </c>
+      <c r="G378" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
         <v>529</v>
       </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C380" t="inlineStr">
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
         <is>
           <t>Indústria 4.0</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr">
+      <c r="D379" t="inlineStr">
         <is>
           <t>Inteligência Artificial (IA - Artificial Intelligence)</t>
         </is>
       </c>
-      <c r="E380" t="inlineStr">
+      <c r="E379" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
@@ -22006,6 +22003,58 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F379" t="n">
+        <v>0</v>
+      </c>
+      <c r="G379" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Machine Learning (ML) / Aprendizado de Máquina</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;subcampo da IA focado em algoritmos que aprendem empiricamente com os dados&lt;/li&gt;
+            &lt;li&gt;permite que os sistemas melhorem o seu desempenho sem programação explícita para cada nova situação&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;coração da manutenção preditiva, cruzando dados históricos para prever falhas antes que ocorram&lt;/li&gt;
+            &lt;li&gt;identificação de padrões ocultos e anomalias em grandes volumes de informação gerados pelo &lt;i&gt;Big Data&lt;/i&gt;&lt;/li&gt;
+            &lt;li&gt;ajuste autônomo e contínuo de parâmetros de maquinário para maximizar o rendimento e minimizar perdas&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na logística 4.0&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;precisão na previsão da demanda, roteirização dinâmica e manutenção preditiva de frotas&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F380" t="n">
         <v>0</v>
       </c>
@@ -22015,7 +22064,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -22024,37 +22073,463 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Logística 4.0</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;otimização da cadeia de suprimentos por meio do uso intensivo de tecnologias digitais&lt;/li&gt;
+            &lt;li&gt;incorporação das inovações da Indústria 4.0 aos processos de movimentação e armazenagem&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Objetivos&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;melhoria contínua e automação dos processos&lt;/li&gt;
+            &lt;li&gt;maior integração entre as etapas da cadeia&lt;/li&gt;
+            &lt;li&gt;visibilidade e rastreabilidade de ponta a ponta em tempo real&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>0</v>
+      </c>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>532</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
           <t>Indústria 4.0</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>Machine Learning (ML) / Aprendizado de Máquina</t>
-        </is>
-      </c>
-      <c r="E381" t="inlineStr">
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Processamento de Linguagem Natural (NLP)</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
         &lt;ul&gt;
-            &lt;li&gt;subcampo da IA focado em algoritmos que aprendem empiricamente com os dados&lt;/li&gt;
-            &lt;li&gt;permite que os sistemas melhorem o seu desempenho sem programação explícita para cada nova situação&lt;/li&gt;
+            &lt;li&gt;vertente da inteligência artificial focada na interação entre computadores e a linguagem humana&lt;/li&gt;
+            &lt;li&gt;capacita sistemas a ler, interpretar, compreender e gerar texto ou voz de forma contextual&lt;/li&gt;
         &lt;/ul&gt;
     &lt;/li&gt;
-    &lt;li&gt;&lt;b&gt;Impacto na produção&lt;/b&gt;
-        &lt;ul&gt;
-            &lt;li&gt;coração da manutenção preditiva, cruzando dados históricos para prever falhas antes que ocorram&lt;/li&gt;
-            &lt;li&gt;identificação de padrões ocultos e anomalias em grandes volumes de informação gerados pelo &lt;i&gt;Big Data&lt;/i&gt;&lt;/li&gt;
-            &lt;li&gt;ajuste autónomo e contínuo de parâmetros de maquinário para maximizar o rendimento e minimizar perdas&lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto na logística 4.0&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;automação do atendimento ao cliente via &lt;i&gt;chatbots&lt;/i&gt; e assistentes virtuais&lt;/li&gt;
+            &lt;li&gt;extração e estruturação automatizada de dados em conhecimentos de transporte, notas fiscais e contratos&lt;/li&gt;
         &lt;/ul&gt;
     &lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F381" t="n">
-        <v>0</v>
-      </c>
-      <c r="G381" t="n">
+      <c r="F382" t="n">
+        <v>0</v>
+      </c>
+      <c r="G382" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>533</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Outsourcing (Terceirização)</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;processo de gestão focado na contratação de parceiros externos (como Operadores Logísticos) para executar atividades da cadeia&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Impacto&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;direcionamento do foco da empresa contratante para o seu &lt;i&gt;core business&lt;/i&gt; (atividade-fim ou negócio principal)&lt;/li&gt;
+            &lt;li&gt;conversão de custos fixos com frota e armazéns próprios em custos variáveis&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Atenção em provas&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;é uma estratégia de gestão e delegação de serviços, não uma ferramenta digital de análise de dados massivos&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>0</v>
+      </c>
+      <c r="G383" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>534</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Blockchain (Corrente de Blocos)</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;tecnologia que oferece um registro imutável, descentralizado e transparente de transações&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Aplicação na logística&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;rastreamento inviolável de produtos e verificação de sua procedência de ponta a ponta&lt;/li&gt;
+            &lt;li&gt;melhoria drástica da visibilidade e da segurança das operações logísticas&lt;/li&gt;
+            &lt;li&gt;simplificação de processos de pagamento e documentação via &lt;i&gt;smart contracts&lt;/i&gt; (contratos inteligentes)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>0</v>
+      </c>
+      <c r="G384" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>535</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Indústria 4.0</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Realidade Aumentada (AR - Augmented Reality)</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;sobreposição de informações digitais (gráficos, hologramas, textos) ao ambiente físico do usuário em tempo real&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Aplicação na logística&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;sistemas de &lt;i&gt;picking&lt;/i&gt; (separação de pedidos) guiados por óculos inteligentes&lt;/li&gt;
+            &lt;li&gt;identificação rápida de prateleiras e lotes no armazém sem uso das mãos&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Atenção em provas&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;não é a rede de objetos físicos conectados, mas a interface visual sobreposta ao mundo real&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>0</v>
+      </c>
+      <c r="G385" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>536</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Métodos de Taguchi (Engenharia Robusta)</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Propósito Principal&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;projetar produtos e processos imunes ou insensíveis a fontes de ruído e perturbações externas (robustez)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Conceitos-Chave&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;&lt;b&gt;Design Robusto:&lt;/b&gt; focado em minimizar a sensibilidade às variações do ambiente e de fabricação sem eliminar as causas na raiz (que seriam muito caras)&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;Função Perda da Qualidade (FPQ):&lt;/b&gt; demonstra que qualquer desvio em relação ao valornominal gera prejuízo à sociedade, aumentando proporcionalmente ao quadrado da distância da especificação ideal&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;Planejamento de Experimentos (DoE):&lt;/b&gt; uso de matrizes ortogonais para testar múltiplos fatores simultaneamente com baixo custo&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>0</v>
+      </c>
+      <c r="G386" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>537</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Engenharia de Produto</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Pacote de Produtos e Serviços</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Definição Conceitual&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;corresponde à combinação integrada de bens tangíveis (produtos) e intangíveis (serviços) que a organização oferece coletivamente aos seus clientes&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Importância na Gestão de Operações&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;muitos produtos físicos são vendidos em conjunto com serviços associados (manutenção, garantia, suporte), assim como serviços dependem de bens facilitadores&lt;/li&gt;
+            &lt;li&gt;a gestão integrada do pacote define a posição competitiva e a proposta de valor da empresa no mercado&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>538</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Gestão da Informação</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Sistemas de Informação Gerencial (SIG)</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Conceito e Escopo&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;categoria específica de Sistema de Informação (SI) focada no nível tático da organização&lt;/li&gt;
+            &lt;li&gt;processa dados internos para resumir e relatar o desempenho básico da empresa&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Fatores Críticos de Sucesso&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;envolvimento adequado da alta e média administração para alinhamento estratégico&lt;/li&gt;
+            &lt;li&gt;competência técnica e operacional das pessoas envolvidas no uso e gestão do sistema&lt;/li&gt;
+            &lt;li&gt;foco na informação estruturada para fundamentar a tomada de decisão racional, objetiva e baseada em fatos (evitando dependência de intuição pura)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>539</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Série ISO 9000 (Escopo e Aplicação)</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Propósito Principal&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;estabelecer fundamentos, vocabulário e requisitos para &lt;b&gt;Sistemas de Gestão da Qualidade (SGQ)&lt;/b&gt;&lt;/li&gt;
+            &lt;li&gt;foco na padronização de processos, melhoria contínua e satisfação do cliente&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Abrangência e Aplicação&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;aplicável de forma universal a organizações de todos os tipos e tamanhos (indústrias, comércio, serviços públicos e privados)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Atenção em Provas (Pegadinhas Cebraspe)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;a norma &lt;b&gt;não&lt;/b&gt; restringe seu foco nem serve para orientar exclusivamente "áreas de recursos humanos e computacionais"&lt;/li&gt;
+            &lt;li&gt;não impõe tecnologias específicas ou modelos únicos de gestão de pessoas; foca no resultado do processo e na entrega da qualidade prometida&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>0</v>
+      </c>
+      <c r="G389" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Evolução da Qualidade (As 4 Eras de Garvin)</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;1. Era da Inspeção (Até a década de 1930 - Foco no Produto Final)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;observação direta do produto apenas ao final do processo produtivo&lt;/li&gt;
+            &lt;li&gt;separação rigorosa entre produtos bons e defeituosos (ação estritamente corretiva)&lt;/li&gt;
+            &lt;li&gt;qualidade vista como um problema a ser "filtrado", não prevenido&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;2. Era do Controle Estatístico da Qualidade (Décadas de 1930 a 1950 - Foco no Processo)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;introdução da inspeção baseada em &lt;b&gt;amostras&lt;/b&gt; (cujas propriedades são inferidas/estendidas ao lote inteiro)&lt;/li&gt;
+            &lt;li&gt;foco em localizar e reduzir desvios, defeitos ou falhas durante o processo produtivo, comparando com padrões&lt;/li&gt;
+            &lt;li&gt;criação de &lt;b&gt;departamentos exclusivos&lt;/b&gt; e especializados para administrar os programas de qualidade&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;3. Era da Garantia da Qualidade (Décadas de 1950 a 1980 - Foco no Sistema)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;deslocamento definitivo da detecção para a prevenção (evitar o erro antes que ele ocorra)&lt;/li&gt;
+            &lt;li&gt;qualidade envolve todos os departamentos (manuais, custos da qualidade e auditorias)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;4. Gestão da Qualidade Total - TQM (A partir da década de 1980 - Foco Estratégico e no Cliente)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;&lt;b&gt;visão sistêmica:&lt;/b&gt; qualidade garantida desde a origem dos insumos (fornecedores) até o usuário final&lt;/li&gt;
+            &lt;li&gt;o foco é o consumidor: o produto ou serviço é definido estritamente com base nos interesses do usuário&lt;/li&gt;
+            &lt;li&gt;integração com filosofias de fluxo contínuo e sincronia da produção (como o &lt;i&gt;Just in Time&lt;/i&gt; e o &lt;i&gt;Kanban&lt;/i&gt;)&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>0</v>
+      </c>
+      <c r="G390" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G390"/>
+  <dimension ref="A1:G393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1668,8 +1668,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>64</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1683,12 +1685,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Fórmula do IDC</t>
+          <t>Gerenciamento de Valor Agregado (EVM)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IDC = Valor agregado/Custo real</t>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Métricas Base (Os Pilares)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;&lt;b&gt;Valor Planeado (VP / &lt;i&gt;PV&lt;/i&gt;):&lt;/b&gt; orçamento autorizado para o trabalho programado (o que deveria ter sido feito).&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;Valor Agregado (VA / &lt;i&gt;EV&lt;/i&gt;):&lt;/b&gt; medida do trabalho efetivamente realizado, expressa em termos do orçamento autorizado (o que foi entregue).&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;Custo Real (CR / &lt;i&gt;AC&lt;/i&gt;):&lt;/b&gt; custo total incorrido para realizar o trabalho (o que foi gasto).&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Análise de Variação (Foco nos Desvios)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;&lt;b&gt;Variação de Prazo (VPr / &lt;i&gt;SV&lt;/i&gt;):&lt;/b&gt; mede o desempenho do cronograma financeiro. &lt;br&gt;Fórmula: $SV = VA - VP$ (Se $&lt; 0$, projeto atrasado).&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;Variação de Custos (VC / &lt;i&gt;CV&lt;/i&gt;):&lt;/b&gt; mede o desempenho financeiro do orçamento. &lt;br&gt;Fórmula: $CV = VA - CR$ (Se $&lt; 0$, projeto acima do orçamento).&lt;/li&gt;
+            &lt;li&gt;&lt;i&gt;Nota de memorização:&lt;/i&gt; A fórmula de variação começa sempre pelo Valor Agregado ($VA$).&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Análise de Índices de Desempenho (Foco na Eficiência)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;&lt;b&gt;Índice de Desempenho de Prazo (IDP / &lt;i&gt;SPI&lt;/i&gt;):&lt;/b&gt; &lt;br&gt;Fórmula: $SPI = VA \div VP$ (Se $&lt; 1$, ritmo inferior ao planeado).&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;Índice de Desempenho de Custos (IDC / &lt;i&gt;CPI&lt;/i&gt;):&lt;/b&gt; &lt;br&gt;Fórmula: $CPI = VA \div CR$ (Se $&lt; 1$, custo superior ao planeado).&lt;/li&gt;
+            &lt;li&gt;&lt;i&gt;Nota de memorização:&lt;/i&gt; A fórmula de índice usa divisão, mantendo o Valor Agregado ($VA$) no numerador.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -14111,10 +14135,11 @@
       &lt;li&gt;&lt;strong&gt;CRM (Customer Relationship Management):&lt;/strong&gt; Gestão do relacionamento com o cliente.&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Dica para Petrobras/ANSA:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;O Cebraspe adora afirmar que um SI é composto &lt;u&gt;apenas&lt;/u&gt; por hardware e software. O item estará &lt;strong&gt;ERRADO&lt;/strong&gt;, pois ignora as dimensões Organizacional e Humana.&lt;/li&gt;
-      &lt;li&gt;Fique atento à diferença entre &lt;strong&gt;Dado&lt;/strong&gt; (fato bruto) e &lt;strong&gt;Informação&lt;/strong&gt; (dado modelado para ser útil).&lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Diferenciações Importantes&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Sistema de Informação (SI) vs. Sistema Informatizado:&lt;/strong&gt; O "Sistema Informatizado" é exclusivamente a infraestrutura de TI (hardware e software), atuando apenas como a &lt;u&gt;ferramenta ou meio&lt;/u&gt;. O "Sistema de Informação" é o todo (pessoas, processos, dados e tecnologia) e pode existir até de forma totalmente manual.&lt;/li&gt;
+      &lt;li&gt;Afirmar que um SI é composto &lt;u&gt;apenas&lt;/u&gt; por hardware e software é &lt;strong&gt;ERRADO&lt;/strong&gt;, pois ignora obrigatoriamente as dimensões Organizacional e Humana.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Dado vs. Informação:&lt;/strong&gt; Dado é o fato bruto; Informação é o dado modelado e com significado útil.&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -21082,8 +21107,10 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="n">
-        <v>512</v>
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -21125,6 +21152,13 @@
                     &lt;ul&gt;
                         &lt;li&gt;EVA = Lucro operacional líquido de impostos - (Custo de capital × Capital investido)&lt;/li&gt;
                         &lt;li&gt;EVA = Capital investido × (Retorno sobre o capital - Custo do capital)&lt;/li&gt;
+                    &lt;/ul&gt;
+                &lt;/li&gt;
+&lt;li&gt;&lt;b&gt;Interpretação para Provas:&lt;/b&gt;
+                    &lt;ul&gt;
+                        &lt;li&gt;&lt;b&gt;EVA &gt; 0 (Positivo):&lt;/b&gt; o projeto &lt;b&gt;adiciona (cria) valor&lt;/b&gt; à empresa, pois o retorno supera o custo de oportunidade.&lt;/li&gt;
+                        &lt;li&gt;&lt;b&gt;EVA &lt; 0 (Negativo):&lt;/b&gt; o projeto &lt;b&gt;destrói valor&lt;/b&gt;, pois rende menos do que renderia uma aplicação livre de risco (ex: Títulos Públicos).&lt;/li&gt;
+                        &lt;li&gt;O volume do investimento inicial, por si só, não determina se destrói valor, mas sim o &lt;i&gt;spread&lt;/i&gt; (diferença) de retorno.&lt;/li&gt;
                     &lt;/ul&gt;
                 &lt;/li&gt;
             &lt;/ul&gt;
@@ -22533,6 +22567,159 @@
         <v>0</v>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>541</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Planejamento e Controle da Produção</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Capacidade Produtiva: Hierarquia e Eficiências</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;As 3 Capacidades (Modelo de Desconto de Intervalos)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;&lt;b&gt;1. Capacidade Instalada (ou Projetada):&lt;/b&gt; O máximo absoluto e teórico. Considera o funcionamento ininterrupto da planta (24 horas por dia, 7 dias por semana, 365 dias no ano), sem nenhuma pausa.&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;2. Capacidade Disponível:&lt;/b&gt; É a Capacidade Instalada &lt;u&gt;menos&lt;/u&gt; as &lt;b&gt;Paradas Planejadas&lt;/b&gt;. Aqui se desconta os fins de semana, feriados, turnos inativos, intervalos de refeição e manutenções preventivas programadas.&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;3. Capacidade Efetiva (ou Realizada):&lt;/b&gt; É a Capacidade Disponível &lt;u&gt;menos&lt;/u&gt; as &lt;b&gt;Paradas Não Planejadas&lt;/b&gt;. Aqui se desconta o que deu errado na operação: quebras de máquina (manutenção corretiva), absenteísmo, falta de insumos, refugos e falhas de setup.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Os 2 Índices de Desempenho (Eficiências)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;&lt;b&gt;Grau de Disponibilidade:&lt;/b&gt; Mede o quanto do tempo total (potencial) a empresa realmente se programou para trabalhar. &lt;br&gt;Fórmula: $Capacidade\ Disponível \div Capacidade\ Instalada$&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;Grau de Eficiência:&lt;/b&gt; Mede o quanto do tempo que estava disponível foi efetivamente convertido em produção real. &lt;br&gt;Fórmula: $Capacidade\ Efetiva \div Capacidade\ Disponível$&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;i&gt;Nota de Prova: Algumas bancas cobram o &lt;b&gt;Grau de Utilização&lt;/b&gt;, que é a relação direta entre o que saiu no final e o máximo teórico inicial ($Capacidade\ Efetiva \div Capacidade\ Instalada$).&lt;/i&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>0</v>
+      </c>
+      <c r="G391" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>542</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Contabilidade De Custos</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Apuração Do Custo De Produção</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Apuração de Custos: Fórmulas de CPP, CPA e CPV</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;O Filtro de Custeio (Regra de Ouro)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;apenas gastos de &lt;b&gt;Fábrica/Produção&lt;/b&gt; são Custos.&lt;/li&gt;
+            &lt;li&gt;gastos com Administração, Vendas e Financeiros são &lt;b&gt;Despesas&lt;/b&gt;. Eles NUNCA entram no custo do produto, devendo ser ignorados em cálculos de Custo de Produção.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;1. Material Consumido (MP)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;$MP = Estoque\ Inicial + Compras - Estoque\ Final$&lt;/li&gt;
+            &lt;li&gt;(lembrete: fretes, seguros e tributos não recuperáveis &lt;b&gt;somam-se&lt;/b&gt; ao valor de compra da MP).&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;2. Custo de Produção do Período (CPP)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;soma de todo o esforço fabril do mês.&lt;/li&gt;
+            &lt;li&gt;$CPP = MP\ (Material) + MOD\ (Mão\ de\ Obra) + CIF\ (Custos\ Indiretos)$&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;3. Custo da Produção Acabada (CPA)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;valor dos itens que saíram da linha e foram para o estoque de produtos prontos.&lt;/li&gt;
+            &lt;li&gt;$CPA = Estoque\ Inicial\ em\ Elaboração + CPP - Estoque\ Final\ em\ Elaboração$&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;4. Custo dos Produtos Vendidos (CPV)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;o que foi efetivamente faturado.&lt;/li&gt;
+            &lt;li&gt;$CPV = Estoque\ Inicial\ de\ Acabados + CPA - Estoque\ Final\ de\ Acabados$&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>0</v>
+      </c>
+      <c r="G392" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>543</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Regime de Competência e Regime de Caixa</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Regimes Contábeis: Competência vs. Caixa</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Regime de Competência (Fato Gerador)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;reconhece receitas e despesas &lt;b&gt;no momento exato em que ocorrem&lt;/b&gt; (ex: entrega da mercadoria ou emissão da nota), independentemente de quando o dinheiro efetivamente muda de mãos.&lt;/li&gt;
+            &lt;li&gt;é o regime oficial exigido pela legislação para a elaboração de balanços (DRE, Balanço Patrimonial).&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Regime de Caixa (Fluxo Financeiro)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;reconhece entradas e saídas apenas &lt;b&gt;quando o dinheiro efetivamente transita na conta bancária ou no caixa&lt;/b&gt; (desembolso ou recebimento real).&lt;/li&gt;
+            &lt;li&gt;usado exclusivamente em ferramentas gerenciais de controle de liquidez, como a Demonstração dos Fluxos de Caixa (DFC).&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;i&gt;Nota Teórica: Qualquer divergência temporal de valores no mesmo mês entre o setor de Operações/Compras (que usa Competência) e o setor Financeiro (que usa Caixa) é fruto de vendas ou compras a prazo.&lt;/i&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>0</v>
+      </c>
+      <c r="G393" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G393"/>
+  <dimension ref="A1:G399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13857,8 +13857,10 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="n">
-        <v>354</v>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -13878,23 +13880,25 @@
       <c r="E231" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Conceitos de Verbo para o Cebraspe&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Pretérito Perfeito do Subjuntivo (Tenha Prevalecido):&lt;/strong&gt; Expressa um fato passado concluído em relação a um momento presente.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Presente do Indicativo (É):&lt;/strong&gt; Utilizado aqui para expressar uma definição conceitual e permanente (Presente Atemporal).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Desconstruindo a Pegadinha&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Presente Histórico:&lt;/strong&gt; &lt;u&gt;Não ocorre&lt;/u&gt; neste texto. Ele serve para "trazer o passado para o presente" em narrações, o que não é o caso de um manual técnico.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Paralelismo Temporal:&lt;/strong&gt; Não exige que todos os verbos estejam no mesmo tempo, mas sim que a relação entre eles seja lógica. No texto, a relação é: "Embora algo tenha ocorrido (passado), o fato é (presente)...".&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Dica de Ouro:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Sempre que a banca afirmar que um verbo é "Presente Histórico", verifique se o texto está contando uma história antiga. Se for um texto dissertativo/informativo como este, quase nunca será presente histórico.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;1. Presente Pontual ou Habitual&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Indica uma ação que ocorre no momento da fala ou uma rotina/hábito contínuo.&lt;/li&gt;
+            &lt;li&gt;&lt;i&gt;Exemplo:&lt;/i&gt; "Eu &lt;b&gt;estudo&lt;/b&gt; todos os dias para o concurso."&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;2. Presente Atemporal (Verdade Universal / Validade Permanente)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Indica fatos incontestáveis, leis científicas, provérbios ou afirmações filosóficas. &lt;b&gt;Atribui validade permanente à afirmação.&lt;/b&gt;&lt;/li&gt;
+            &lt;li&gt;&lt;i&gt;Exemplos:&lt;/i&gt; "A água &lt;b&gt;ferve&lt;/b&gt; a 100 graus." / "O tempo é um imperador que &lt;b&gt;diz&lt;/b&gt; que &lt;b&gt;passa&lt;/b&gt;, quando quem passa &lt;b&gt;somos&lt;/b&gt; nós."&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;3. Presente Histórico&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Utiliza o tempo presente para narrar, com maior vivacidade e proximidade, fatos que já aconteceram e foram concluídos no passado.&lt;/li&gt;
+            &lt;li&gt;&lt;i&gt;Exemplo:&lt;/i&gt; "Em 1500, Cabral &lt;b&gt;chega&lt;/b&gt; ao Brasil e &lt;b&gt;descobre&lt;/b&gt; novas terras."&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;Dica de Ouro:&lt;/b&gt; Se for um texto técnico, dissertativo ou legal, dificilmente será presente histórico. Este recurso é típico de narrativas e crónicas.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -22720,6 +22724,257 @@
         <v>0</v>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>544</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Contratação</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Lei 13.303 - 2016</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Dispensa de Licitação: Contratação de Remanescente</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;É &lt;b&gt;dispensável&lt;/b&gt; a licitação para contratação de remanescente de obra, serviço ou fornecimento decorrente de rescisão contratual ou distrato.&lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Requisitos obrigatórios para o novo contratado:&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Respeitar a &lt;b&gt;ordem de classificação&lt;/b&gt; da licitação anterior.&lt;/li&gt;
+            &lt;li&gt;Aceitar as &lt;b&gt;mesmas condições&lt;/b&gt; do contrato encerrado.&lt;/li&gt;
+            &lt;li&gt;Manter obrigatoriamente o &lt;b&gt;preço&lt;/b&gt;, devidamente corrigido.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>0</v>
+      </c>
+      <c r="G394" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>545</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Estatística</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Regressão Linear Múltipla</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Regressão Linear Múltipla: Equação, Pressupostos e Multicolinearidade</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Equação:&lt;/b&gt; $Y = \alpha + \beta_1 x_1 + \beta_2 x_2 + ... + \beta_k x_k + \epsilon$. Baseia-se no princípio &lt;i&gt;ceteris paribus&lt;/i&gt;, em que se estima o efeito de uma variável independente mantendo os outros fatores fixos.&lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Pressupostos dos Erros ($\epsilon$):&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Média nula: $E(\epsilon_i) = 0$.&lt;/li&gt;
+            &lt;li&gt;Homocedasticidade: a variância do erro deve ser constante, independentemente do valor de $X$ ($Var(\epsilon_i) = \sigma^2$).&lt;/li&gt;
+            &lt;li&gt;Ausência de autocorrelação: os erros cometidos pelo modelo são independentes e não se correlacionam ($corr(\epsilon_i, \epsilon_j) = 0$).&lt;/li&gt;
+            &lt;li&gt;Normalidade: os erros têm distribuição normal.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Multicolinearidade:&lt;/b&gt; Ocorre quando há relação linear (alta correlação) entre as variáveis independentes, o que pode tornar a estimativa dos parâmetros insignificante.&lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Graus de Liberdade (GL):&lt;/b&gt; Para $p$ parâmetros estimados (incluindo o intercepto), o GL do Modelo é $p-1$, o GL dos Resíduos é $n-p$ e o GL Total é $n-1$.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>0</v>
+      </c>
+      <c r="G395" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>546</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Estatística</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Regressão Linear Múltipla</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Variáveis Binárias (Dummies)</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Conceito:&lt;/b&gt; Assumem valores $0$ ou $1$ e são utilizadas para indicar a presença ou ausência de uma característica, incorporando aspetos qualitativos ao modelo (ex: sexo, estações do ano).&lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Regra das Categorias:&lt;/b&gt; Para representar uma variável qualitativa com $n$ categorias, é necessário utilizar $n - 1$ variáveis binárias (a exclusão de uma categoria serve de referência para evitar ponderações arbitrárias).&lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Aplicação:&lt;/b&gt; Quando incluídas diretamente no modelo, objetivam estimar diferenças no intercepto. Se usadas interagindo com outras variáveis explicativas, objetivam indicar diferenças na inclinação da reta de regressão para diferentes grupos.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>0</v>
+      </c>
+      <c r="G396" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>547</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Estatística</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Regressão Linear Múltipla</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Problema da Especificação e Teste RESET (Ramsey)</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Problema de Especificação:&lt;/b&gt; Erro na escolha do modelo matemático (linear, exponencial, polinomial) ou falha na determinação de quais variáveis independentes devem ser incluídas.
+        &lt;ul&gt;
+            &lt;li&gt;&lt;b&gt;Omissão de variável relevante:&lt;/b&gt; Torna as estimativas dos parâmetros tendenciosas (enviesadas).&lt;/li&gt;
+            &lt;li&gt;&lt;b&gt;Inclusão de variável desnecessária (irrelevante):&lt;/b&gt; As estimativas permanecem não-tendenciosas, mas a variância dos estimadores é aumentada.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Teste RESET (Ramsey):&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Adiciona polinómios quadráticos e cúbicos aos valores estimados pelo método dos mínimos quadrados (MQO) para detetar erros de especificação ou ausência de não linearidades importantes.&lt;/li&gt;
+            &lt;li&gt;Hipótese Nula ($H_0$): indica que o modelo original foi especificado corretamente. Rejeitar $H_0$ (quando $F_{calculado} &gt; F_{critico}$) significa que há erro de especificação.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>0</v>
+      </c>
+      <c r="G397" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>548</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Estatística</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Regressão Linear Múltipla</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Transformação de Box-Cox</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Objetivo:&lt;/b&gt; É uma transformação de potência aplicada para corrigir a não normalidade dos dados e estabilizar a variância, corrigindo a heterocedasticidade.&lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Fórmula Base:&lt;/b&gt; $X^{(\lambda)} = \frac{X^\lambda - 1}{\lambda}$ ou simplificadamente $X^\lambda$ (para $\lambda \neq 0$).&lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Caso Especial:&lt;/b&gt; Quando o parâmetro $\lambda = 0$, a transformação aplicada deve ser logarítmica ($X^{(0)} = \log(X)$).&lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Condição:&lt;/b&gt; A transformação de Box e Cox é definida apenas para variáveis com valores estritamente positivos ($X &gt; 0$).&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>0</v>
+      </c>
+      <c r="G398" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>549</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Semântica</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Reescritura: Invenção de Nexo, Modalização e Esvaziamento Semântico</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;&lt;b&gt;Invenção de Nexo (Relação Lógica Inexistente)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Transformar duas orações independentes (fatos que somam forças) em uma relação de subordinação (inserindo conectivos de causa/condição como &lt;i&gt;"considerando"&lt;/i&gt; ou &lt;i&gt;"já que"&lt;/i&gt;). Isso cria uma relação de dependência que o autor não escreveu.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Mudança de Modalização (Fato vs. Opinião)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Trocar uma afirmação categórica/objetiva (ex: &lt;i&gt;"é um sucesso"&lt;/i&gt;) por uma expressão de percepção ou consenso social (ex: &lt;i&gt;"já são aceitas como um sucesso"&lt;/i&gt;). Isso enfraquece a certeza da frase original.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;li&gt;&lt;b&gt;Esvaziamento Semântico (Omissão de Palavras-Chave)&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Retirar adjetivos ou advérbios com peso argumentativo (ex: &lt;i&gt;"comprovado"&lt;/i&gt;, &lt;i&gt;"sempre"&lt;/i&gt;) atenua o argumento e constitui erro direto de sentido.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+    &lt;hr&gt;
+    &lt;li&gt;&lt; ATENÇÃO: Particularidade CEBRASPE (Visão de "Coerência Global")&lt;/b&gt;
+        &lt;ul&gt;
+            &lt;li&gt;Para o Cebraspe, cometer os erros acima não altera apenas o "sentido". Eles consideram que isso destrói a &lt;b&gt;macroestrutura argumentativa&lt;/b&gt; do autor e dão o item como ERRADO mesmo que o enunciado pergunte apenas se a &lt;i&gt;"coerência"&lt;/i&gt; foi mantida.&lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>0</v>
+      </c>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
